--- a/artfynd/A 44203-2025 artfynd.xlsx
+++ b/artfynd/A 44203-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128532926</v>
       </c>
       <c r="B2" t="n">
-        <v>92754</v>
+        <v>92760</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44203-2025 artfynd.xlsx
+++ b/artfynd/A 44203-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128532926</v>
       </c>
       <c r="B2" t="n">
-        <v>92760</v>
+        <v>92766</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44203-2025 artfynd.xlsx
+++ b/artfynd/A 44203-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128532926</v>
       </c>
       <c r="B2" t="n">
-        <v>92766</v>
+        <v>92768</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44203-2025 artfynd.xlsx
+++ b/artfynd/A 44203-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128532926</v>
       </c>
       <c r="B2" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44203-2025 artfynd.xlsx
+++ b/artfynd/A 44203-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128532926</v>
       </c>
       <c r="B2" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44203-2025 artfynd.xlsx
+++ b/artfynd/A 44203-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128532926</v>
       </c>
       <c r="B2" t="n">
-        <v>92796</v>
+        <v>92801</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44203-2025 artfynd.xlsx
+++ b/artfynd/A 44203-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128532926</v>
       </c>
       <c r="B2" t="n">
-        <v>92801</v>
+        <v>92806</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44203-2025 artfynd.xlsx
+++ b/artfynd/A 44203-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -778,6 +778,1849 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128944684</v>
+      </c>
+      <c r="B3" t="n">
+        <v>78877</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hästkullen, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>730648</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7400352</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128944682</v>
+      </c>
+      <c r="B4" t="n">
+        <v>78878</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hästkullen, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>730487</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7400456</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128944689</v>
+      </c>
+      <c r="B5" t="n">
+        <v>78877</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hästkullen, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>730363</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7400440</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128944692</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92794</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hästkullen, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>730513</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7400332</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128944683</v>
+      </c>
+      <c r="B7" t="n">
+        <v>78877</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hästkullen, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>730502</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7400296</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128944688</v>
+      </c>
+      <c r="B8" t="n">
+        <v>78877</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hästkullen, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>730461</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7400442</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128944687</v>
+      </c>
+      <c r="B9" t="n">
+        <v>78877</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hästkullen, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>730470</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7400373</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128944690</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91665</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hästkullen, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>730508</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7400458</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128944680</v>
+      </c>
+      <c r="B11" t="n">
+        <v>78878</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hästkullen, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>730648</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7400352</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128944674</v>
+      </c>
+      <c r="B12" t="n">
+        <v>90536</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hästkullen, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>730365</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7400452</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128944686</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78877</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hästkullen, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>730518</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7400367</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128944691</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92794</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hästkullen, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>730498</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7400295</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128944678</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92825</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hästkullen, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>730462</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7400313</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128944673</v>
+      </c>
+      <c r="B16" t="n">
+        <v>90536</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hästkullen, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>730476</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7400283</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128944685</v>
+      </c>
+      <c r="B17" t="n">
+        <v>78877</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Hästkullen, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>730663</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7400366</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128944679</v>
+      </c>
+      <c r="B18" t="n">
+        <v>78878</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hästkullen, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>730482</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7400297</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128944693</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92794</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hästkullen, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>730500</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7400421</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128944681</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78878</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Hästkullen, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>730491</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7400393</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128944672</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91679</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1588</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Violmussling</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Trichaptum laricinum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Hästkullen, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>730429</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7400485</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44203-2025 artfynd.xlsx
+++ b/artfynd/A 44203-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>128532926</v>
       </c>
       <c r="B2" t="n">
-        <v>92806</v>
+        <v>92810</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128944684</v>
       </c>
       <c r="B3" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>128944682</v>
       </c>
       <c r="B4" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>128944689</v>
       </c>
       <c r="B5" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>128944692</v>
       </c>
       <c r="B6" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>128944683</v>
       </c>
       <c r="B7" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1266,32 +1266,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128944688</v>
+        <v>128944690</v>
       </c>
       <c r="B8" t="n">
-        <v>78877</v>
+        <v>91669</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730461</v>
+        <v>730508</v>
       </c>
       <c r="R8" t="n">
-        <v>7400442</v>
+        <v>7400458</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1363,10 +1363,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128944687</v>
+        <v>128944688</v>
       </c>
       <c r="B9" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>730470</v>
+        <v>730461</v>
       </c>
       <c r="R9" t="n">
-        <v>7400373</v>
+        <v>7400442</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1460,32 +1460,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128944690</v>
+        <v>128944687</v>
       </c>
       <c r="B10" t="n">
-        <v>91665</v>
+        <v>78881</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>730508</v>
+        <v>730470</v>
       </c>
       <c r="R10" t="n">
-        <v>7400458</v>
+        <v>7400373</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1560,7 +1560,7 @@
         <v>128944680</v>
       </c>
       <c r="B11" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>128944674</v>
       </c>
       <c r="B12" t="n">
-        <v>90536</v>
+        <v>90540</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>128944686</v>
       </c>
       <c r="B13" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>128944691</v>
       </c>
       <c r="B14" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1945,32 +1945,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128944678</v>
+        <v>128944673</v>
       </c>
       <c r="B15" t="n">
-        <v>92825</v>
+        <v>90540</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>232140</v>
+        <v>1962</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>730462</v>
+        <v>730476</v>
       </c>
       <c r="R15" t="n">
-        <v>7400313</v>
+        <v>7400283</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2042,10 +2042,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128944673</v>
+        <v>128944685</v>
       </c>
       <c r="B16" t="n">
-        <v>90536</v>
+        <v>78881</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2053,21 +2053,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>730476</v>
+        <v>730663</v>
       </c>
       <c r="R16" t="n">
-        <v>7400283</v>
+        <v>7400366</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2139,32 +2139,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128944685</v>
+        <v>128944678</v>
       </c>
       <c r="B17" t="n">
-        <v>78877</v>
+        <v>92829</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>232140</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2174,10 +2174,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>730663</v>
+        <v>730462</v>
       </c>
       <c r="R17" t="n">
-        <v>7400366</v>
+        <v>7400313</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2239,7 +2239,7 @@
         <v>128944679</v>
       </c>
       <c r="B18" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>128944693</v>
       </c>
       <c r="B19" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>128944681</v>
       </c>
       <c r="B20" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>128944672</v>
       </c>
       <c r="B21" t="n">
-        <v>91679</v>
+        <v>91683</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2621,6 +2621,2237 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128970454</v>
+      </c>
+      <c r="B22" t="n">
+        <v>78881</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Hästkullen, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>730523</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7400319</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128970462</v>
+      </c>
+      <c r="B23" t="n">
+        <v>92798</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Hästkullen, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>730496</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7400291</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128970459</v>
+      </c>
+      <c r="B24" t="n">
+        <v>78881</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Hästkullen, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>730475</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7400470</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128970458</v>
+      </c>
+      <c r="B25" t="n">
+        <v>78881</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Hästkullen, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>730489</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7400398</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128970445</v>
+      </c>
+      <c r="B26" t="n">
+        <v>92802</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Hästkullen, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>730387</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7400491</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128970447</v>
+      </c>
+      <c r="B27" t="n">
+        <v>92810</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Hästkullen, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>730515</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7400280</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128970464</v>
+      </c>
+      <c r="B28" t="n">
+        <v>92798</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Hästkullen, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>730526</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7400400</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128970444</v>
+      </c>
+      <c r="B29" t="n">
+        <v>92782</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6055</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Spadskinn</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Stereopsis vitellina</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(S.Lundell) D.A.Reid</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Hästkullen, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>730530</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7400285</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128970461</v>
+      </c>
+      <c r="B30" t="n">
+        <v>92798</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Hästkullen, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>730490</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7400286</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128970443</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79714</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Hästkullen, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>730506</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7400283</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128970456</v>
+      </c>
+      <c r="B32" t="n">
+        <v>78881</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Hästkullen, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>730514</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7400402</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128970460</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79203</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>864</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Hästkullen, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>730589</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7400431</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128970453</v>
+      </c>
+      <c r="B34" t="n">
+        <v>78882</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Hästkullen, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>730495</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7400399</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128970449</v>
+      </c>
+      <c r="B35" t="n">
+        <v>97507</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Hästkullen, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>730553</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7400437</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128970457</v>
+      </c>
+      <c r="B36" t="n">
+        <v>78881</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Hästkullen, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>730492</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7400398</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128970441</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79714</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Hästkullen, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>730604</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7400290</v>
+      </c>
+      <c r="S37" t="n">
+        <v>3</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128970463</v>
+      </c>
+      <c r="B38" t="n">
+        <v>92798</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Hästkullen, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>730531</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7400330</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>128970452</v>
+      </c>
+      <c r="B39" t="n">
+        <v>78882</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Hästkullen, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>730572</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7400289</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>128970455</v>
+      </c>
+      <c r="B40" t="n">
+        <v>78881</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Hästkullen, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>730674</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7400378</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>128970440</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79714</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Hästkullen, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>730523</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7400413</v>
+      </c>
+      <c r="S41" t="n">
+        <v>3</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>128970450</v>
+      </c>
+      <c r="B42" t="n">
+        <v>92993</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Hästkullen, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>730520</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7400447</v>
+      </c>
+      <c r="S42" t="n">
+        <v>3</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>128970442</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79714</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Hästkullen, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>730616</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7400292</v>
+      </c>
+      <c r="S43" t="n">
+        <v>3</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>128970448</v>
+      </c>
+      <c r="B44" t="n">
+        <v>92810</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Hästkullen, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>730503</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7400393</v>
+      </c>
+      <c r="S44" t="n">
+        <v>3</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44203-2025 artfynd.xlsx
+++ b/artfynd/A 44203-2025 artfynd.xlsx
@@ -1751,32 +1751,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128944686</v>
+        <v>128944691</v>
       </c>
       <c r="B13" t="n">
-        <v>78881</v>
+        <v>92798</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>730518</v>
+        <v>730498</v>
       </c>
       <c r="R13" t="n">
-        <v>7400367</v>
+        <v>7400295</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1848,32 +1848,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128944691</v>
+        <v>128944686</v>
       </c>
       <c r="B14" t="n">
-        <v>92798</v>
+        <v>78881</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>730498</v>
+        <v>730518</v>
       </c>
       <c r="R14" t="n">
-        <v>7400295</v>
+        <v>7400367</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1945,32 +1945,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128944673</v>
+        <v>128944678</v>
       </c>
       <c r="B15" t="n">
-        <v>90540</v>
+        <v>92829</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1962</v>
+        <v>232140</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>730476</v>
+        <v>730462</v>
       </c>
       <c r="R15" t="n">
-        <v>7400283</v>
+        <v>7400313</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2042,10 +2042,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128944685</v>
+        <v>128944673</v>
       </c>
       <c r="B16" t="n">
-        <v>78881</v>
+        <v>90540</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2053,21 +2053,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>730663</v>
+        <v>730476</v>
       </c>
       <c r="R16" t="n">
-        <v>7400366</v>
+        <v>7400283</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2139,32 +2139,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128944678</v>
+        <v>128944685</v>
       </c>
       <c r="B17" t="n">
-        <v>92829</v>
+        <v>78881</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>232140</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2174,10 +2174,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>730462</v>
+        <v>730663</v>
       </c>
       <c r="R17" t="n">
-        <v>7400313</v>
+        <v>7400366</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2624,32 +2624,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128970454</v>
+        <v>128970462</v>
       </c>
       <c r="B22" t="n">
-        <v>78881</v>
+        <v>92798</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>730523</v>
+        <v>730496</v>
       </c>
       <c r="R22" t="n">
-        <v>7400319</v>
+        <v>7400291</v>
       </c>
       <c r="S22" t="n">
         <v>3</v>
@@ -2721,32 +2721,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128970462</v>
+        <v>128970454</v>
       </c>
       <c r="B23" t="n">
-        <v>92798</v>
+        <v>78881</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2756,10 +2756,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>730496</v>
+        <v>730523</v>
       </c>
       <c r="R23" t="n">
-        <v>7400291</v>
+        <v>7400319</v>
       </c>
       <c r="S23" t="n">
         <v>3</v>
@@ -3400,32 +3400,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128970461</v>
+        <v>128970456</v>
       </c>
       <c r="B30" t="n">
-        <v>92798</v>
+        <v>78881</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3435,10 +3435,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>730490</v>
+        <v>730514</v>
       </c>
       <c r="R30" t="n">
-        <v>7400286</v>
+        <v>7400402</v>
       </c>
       <c r="S30" t="n">
         <v>3</v>
@@ -3497,32 +3497,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128970443</v>
+        <v>128970461</v>
       </c>
       <c r="B31" t="n">
-        <v>79714</v>
+        <v>92798</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3532,10 +3532,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>730506</v>
+        <v>730490</v>
       </c>
       <c r="R31" t="n">
-        <v>7400283</v>
+        <v>7400286</v>
       </c>
       <c r="S31" t="n">
         <v>3</v>
@@ -3594,10 +3594,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128970456</v>
+        <v>128970443</v>
       </c>
       <c r="B32" t="n">
-        <v>78881</v>
+        <v>79714</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3605,21 +3605,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>730514</v>
+        <v>730506</v>
       </c>
       <c r="R32" t="n">
-        <v>7400402</v>
+        <v>7400283</v>
       </c>
       <c r="S32" t="n">
         <v>3</v>
@@ -3885,32 +3885,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128970449</v>
+        <v>128970457</v>
       </c>
       <c r="B35" t="n">
-        <v>97507</v>
+        <v>78881</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221945</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3920,10 +3920,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>730553</v>
+        <v>730492</v>
       </c>
       <c r="R35" t="n">
-        <v>7400437</v>
+        <v>7400398</v>
       </c>
       <c r="S35" t="n">
         <v>3</v>
@@ -3982,32 +3982,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128970457</v>
+        <v>128970449</v>
       </c>
       <c r="B36" t="n">
-        <v>78881</v>
+        <v>97507</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>221945</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4017,10 +4017,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>730492</v>
+        <v>730553</v>
       </c>
       <c r="R36" t="n">
-        <v>7400398</v>
+        <v>7400437</v>
       </c>
       <c r="S36" t="n">
         <v>3</v>
@@ -4176,32 +4176,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128970463</v>
+        <v>128970452</v>
       </c>
       <c r="B38" t="n">
-        <v>92798</v>
+        <v>78882</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4211,10 +4211,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>730531</v>
+        <v>730572</v>
       </c>
       <c r="R38" t="n">
-        <v>7400330</v>
+        <v>7400289</v>
       </c>
       <c r="S38" t="n">
         <v>3</v>
@@ -4273,32 +4273,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128970452</v>
+        <v>128970463</v>
       </c>
       <c r="B39" t="n">
-        <v>78882</v>
+        <v>92798</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4308,10 +4308,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>730572</v>
+        <v>730531</v>
       </c>
       <c r="R39" t="n">
-        <v>7400289</v>
+        <v>7400330</v>
       </c>
       <c r="S39" t="n">
         <v>3</v>
@@ -4467,10 +4467,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128970440</v>
+        <v>128970450</v>
       </c>
       <c r="B41" t="n">
-        <v>79714</v>
+        <v>92993</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4478,21 +4478,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229821</v>
+        <v>2079</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4502,10 +4502,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>730523</v>
+        <v>730520</v>
       </c>
       <c r="R41" t="n">
-        <v>7400413</v>
+        <v>7400447</v>
       </c>
       <c r="S41" t="n">
         <v>3</v>
@@ -4564,10 +4564,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128970450</v>
+        <v>128970440</v>
       </c>
       <c r="B42" t="n">
-        <v>92993</v>
+        <v>79714</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4575,21 +4575,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2079</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4599,10 +4599,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>730520</v>
+        <v>730523</v>
       </c>
       <c r="R42" t="n">
-        <v>7400447</v>
+        <v>7400413</v>
       </c>
       <c r="S42" t="n">
         <v>3</v>

--- a/artfynd/A 44203-2025 artfynd.xlsx
+++ b/artfynd/A 44203-2025 artfynd.xlsx
@@ -1266,32 +1266,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128944690</v>
+        <v>128944688</v>
       </c>
       <c r="B8" t="n">
-        <v>91669</v>
+        <v>78881</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730508</v>
+        <v>730461</v>
       </c>
       <c r="R8" t="n">
-        <v>7400458</v>
+        <v>7400442</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1363,7 +1363,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128944688</v>
+        <v>128944687</v>
       </c>
       <c r="B9" t="n">
         <v>78881</v>
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>730461</v>
+        <v>730470</v>
       </c>
       <c r="R9" t="n">
-        <v>7400442</v>
+        <v>7400373</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1460,32 +1460,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128944687</v>
+        <v>128944690</v>
       </c>
       <c r="B10" t="n">
-        <v>78881</v>
+        <v>91669</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>730470</v>
+        <v>730508</v>
       </c>
       <c r="R10" t="n">
-        <v>7400373</v>
+        <v>7400458</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1945,32 +1945,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128944678</v>
+        <v>128944673</v>
       </c>
       <c r="B15" t="n">
-        <v>92829</v>
+        <v>90540</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>232140</v>
+        <v>1962</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>730462</v>
+        <v>730476</v>
       </c>
       <c r="R15" t="n">
-        <v>7400313</v>
+        <v>7400283</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2042,10 +2042,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128944673</v>
+        <v>128944685</v>
       </c>
       <c r="B16" t="n">
-        <v>90540</v>
+        <v>78881</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2053,21 +2053,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>730476</v>
+        <v>730663</v>
       </c>
       <c r="R16" t="n">
-        <v>7400283</v>
+        <v>7400366</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2139,32 +2139,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128944685</v>
+        <v>128944678</v>
       </c>
       <c r="B17" t="n">
-        <v>78881</v>
+        <v>92829</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>232140</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2174,10 +2174,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>730663</v>
+        <v>730462</v>
       </c>
       <c r="R17" t="n">
-        <v>7400366</v>
+        <v>7400313</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -4079,32 +4079,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128970441</v>
+        <v>128970463</v>
       </c>
       <c r="B37" t="n">
-        <v>79714</v>
+        <v>92798</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4114,10 +4114,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>730604</v>
+        <v>730531</v>
       </c>
       <c r="R37" t="n">
-        <v>7400290</v>
+        <v>7400330</v>
       </c>
       <c r="S37" t="n">
         <v>3</v>
@@ -4176,10 +4176,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128970452</v>
+        <v>128970441</v>
       </c>
       <c r="B38" t="n">
-        <v>78882</v>
+        <v>79714</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4187,21 +4187,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4211,10 +4211,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>730572</v>
+        <v>730604</v>
       </c>
       <c r="R38" t="n">
-        <v>7400289</v>
+        <v>7400290</v>
       </c>
       <c r="S38" t="n">
         <v>3</v>
@@ -4273,32 +4273,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128970463</v>
+        <v>128970452</v>
       </c>
       <c r="B39" t="n">
-        <v>92798</v>
+        <v>78882</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4308,10 +4308,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>730531</v>
+        <v>730572</v>
       </c>
       <c r="R39" t="n">
-        <v>7400330</v>
+        <v>7400289</v>
       </c>
       <c r="S39" t="n">
         <v>3</v>
@@ -4467,10 +4467,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128970450</v>
+        <v>128970440</v>
       </c>
       <c r="B41" t="n">
-        <v>92993</v>
+        <v>79714</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4478,21 +4478,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2079</v>
+        <v>229821</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4502,10 +4502,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>730520</v>
+        <v>730523</v>
       </c>
       <c r="R41" t="n">
-        <v>7400447</v>
+        <v>7400413</v>
       </c>
       <c r="S41" t="n">
         <v>3</v>
@@ -4564,10 +4564,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128970440</v>
+        <v>128970450</v>
       </c>
       <c r="B42" t="n">
-        <v>79714</v>
+        <v>92993</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4575,21 +4575,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229821</v>
+        <v>2079</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4599,10 +4599,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>730523</v>
+        <v>730520</v>
       </c>
       <c r="R42" t="n">
-        <v>7400413</v>
+        <v>7400447</v>
       </c>
       <c r="S42" t="n">
         <v>3</v>

--- a/artfynd/A 44203-2025 artfynd.xlsx
+++ b/artfynd/A 44203-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128532926</v>
       </c>
       <c r="B2" t="n">
-        <v>92810</v>
+        <v>92815</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128944684</v>
+        <v>128944682</v>
       </c>
       <c r="B3" t="n">
-        <v>78881</v>
+        <v>78787</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730648</v>
+        <v>730487</v>
       </c>
       <c r="R3" t="n">
-        <v>7400352</v>
+        <v>7400456</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -878,10 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128944682</v>
+        <v>128944684</v>
       </c>
       <c r="B4" t="n">
-        <v>78882</v>
+        <v>78786</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -889,21 +889,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730487</v>
+        <v>730648</v>
       </c>
       <c r="R4" t="n">
-        <v>7400456</v>
+        <v>7400352</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -978,7 +978,7 @@
         <v>128944689</v>
       </c>
       <c r="B5" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>128944692</v>
       </c>
       <c r="B6" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>128944683</v>
       </c>
       <c r="B7" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1266,32 +1266,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128944688</v>
+        <v>128944690</v>
       </c>
       <c r="B8" t="n">
-        <v>78881</v>
+        <v>91674</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730461</v>
+        <v>730508</v>
       </c>
       <c r="R8" t="n">
-        <v>7400442</v>
+        <v>7400458</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1363,10 +1363,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128944687</v>
+        <v>128944688</v>
       </c>
       <c r="B9" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>730470</v>
+        <v>730461</v>
       </c>
       <c r="R9" t="n">
-        <v>7400373</v>
+        <v>7400442</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1460,32 +1460,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128944690</v>
+        <v>128944687</v>
       </c>
       <c r="B10" t="n">
-        <v>91669</v>
+        <v>78786</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>730508</v>
+        <v>730470</v>
       </c>
       <c r="R10" t="n">
-        <v>7400458</v>
+        <v>7400373</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1560,7 +1560,7 @@
         <v>128944680</v>
       </c>
       <c r="B11" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1654,32 +1654,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128944674</v>
+        <v>128944691</v>
       </c>
       <c r="B12" t="n">
-        <v>90540</v>
+        <v>92803</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>730365</v>
+        <v>730498</v>
       </c>
       <c r="R12" t="n">
-        <v>7400452</v>
+        <v>7400295</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1751,32 +1751,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128944691</v>
+        <v>128944674</v>
       </c>
       <c r="B13" t="n">
-        <v>92798</v>
+        <v>90545</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>730498</v>
+        <v>730365</v>
       </c>
       <c r="R13" t="n">
-        <v>7400295</v>
+        <v>7400452</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1851,7 +1851,7 @@
         <v>128944686</v>
       </c>
       <c r="B14" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>128944673</v>
       </c>
       <c r="B15" t="n">
-        <v>90540</v>
+        <v>90545</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2042,32 +2042,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128944685</v>
+        <v>128944678</v>
       </c>
       <c r="B16" t="n">
-        <v>78881</v>
+        <v>92834</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>232140</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>730663</v>
+        <v>730462</v>
       </c>
       <c r="R16" t="n">
-        <v>7400366</v>
+        <v>7400313</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2139,32 +2139,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128944678</v>
+        <v>128944685</v>
       </c>
       <c r="B17" t="n">
-        <v>92829</v>
+        <v>78786</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>232140</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2174,10 +2174,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>730462</v>
+        <v>730663</v>
       </c>
       <c r="R17" t="n">
-        <v>7400313</v>
+        <v>7400366</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2239,7 +2239,7 @@
         <v>128944679</v>
       </c>
       <c r="B18" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>128944693</v>
       </c>
       <c r="B19" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>128944681</v>
       </c>
       <c r="B20" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>128944672</v>
       </c>
       <c r="B21" t="n">
-        <v>91683</v>
+        <v>91688</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>128970462</v>
       </c>
       <c r="B22" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>128970454</v>
       </c>
       <c r="B23" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>128970459</v>
       </c>
       <c r="B24" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>128970458</v>
       </c>
       <c r="B25" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>128970445</v>
       </c>
       <c r="B26" t="n">
-        <v>92802</v>
+        <v>92807</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>128970447</v>
       </c>
       <c r="B27" t="n">
-        <v>92810</v>
+        <v>92815</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>128970464</v>
       </c>
       <c r="B28" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         <v>128970444</v>
       </c>
       <c r="B29" t="n">
-        <v>92782</v>
+        <v>92787</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>128970456</v>
       </c>
       <c r="B30" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3497,32 +3497,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128970461</v>
+        <v>128970443</v>
       </c>
       <c r="B31" t="n">
-        <v>92798</v>
+        <v>79619</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3532,10 +3532,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>730490</v>
+        <v>730506</v>
       </c>
       <c r="R31" t="n">
-        <v>7400286</v>
+        <v>7400283</v>
       </c>
       <c r="S31" t="n">
         <v>3</v>
@@ -3594,32 +3594,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128970443</v>
+        <v>128970461</v>
       </c>
       <c r="B32" t="n">
-        <v>79714</v>
+        <v>92803</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>730506</v>
+        <v>730490</v>
       </c>
       <c r="R32" t="n">
-        <v>7400283</v>
+        <v>7400286</v>
       </c>
       <c r="S32" t="n">
         <v>3</v>
@@ -3691,10 +3691,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128970460</v>
+        <v>128970453</v>
       </c>
       <c r="B33" t="n">
-        <v>79203</v>
+        <v>78787</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3702,21 +3702,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>864</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3726,10 +3726,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>730589</v>
+        <v>730495</v>
       </c>
       <c r="R33" t="n">
-        <v>7400431</v>
+        <v>7400399</v>
       </c>
       <c r="S33" t="n">
         <v>3</v>
@@ -3788,10 +3788,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128970453</v>
+        <v>128970460</v>
       </c>
       <c r="B34" t="n">
-        <v>78882</v>
+        <v>79108</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3799,21 +3799,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>864</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3823,10 +3823,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>730495</v>
+        <v>730589</v>
       </c>
       <c r="R34" t="n">
-        <v>7400399</v>
+        <v>7400431</v>
       </c>
       <c r="S34" t="n">
         <v>3</v>
@@ -3885,32 +3885,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128970457</v>
+        <v>128970449</v>
       </c>
       <c r="B35" t="n">
-        <v>78881</v>
+        <v>97514</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>221945</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3920,10 +3920,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>730492</v>
+        <v>730553</v>
       </c>
       <c r="R35" t="n">
-        <v>7400398</v>
+        <v>7400437</v>
       </c>
       <c r="S35" t="n">
         <v>3</v>
@@ -3982,32 +3982,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128970449</v>
+        <v>128970457</v>
       </c>
       <c r="B36" t="n">
-        <v>97507</v>
+        <v>78786</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221945</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4017,10 +4017,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>730553</v>
+        <v>730492</v>
       </c>
       <c r="R36" t="n">
-        <v>7400437</v>
+        <v>7400398</v>
       </c>
       <c r="S36" t="n">
         <v>3</v>
@@ -4082,7 +4082,7 @@
         <v>128970463</v>
       </c>
       <c r="B37" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4179,7 +4179,7 @@
         <v>128970441</v>
       </c>
       <c r="B38" t="n">
-        <v>79714</v>
+        <v>79619</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4276,7 +4276,7 @@
         <v>128970452</v>
       </c>
       <c r="B39" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4373,7 +4373,7 @@
         <v>128970455</v>
       </c>
       <c r="B40" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4467,10 +4467,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128970440</v>
+        <v>128970450</v>
       </c>
       <c r="B41" t="n">
-        <v>79714</v>
+        <v>92998</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4478,21 +4478,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229821</v>
+        <v>2079</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4502,10 +4502,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>730523</v>
+        <v>730520</v>
       </c>
       <c r="R41" t="n">
-        <v>7400413</v>
+        <v>7400447</v>
       </c>
       <c r="S41" t="n">
         <v>3</v>
@@ -4564,10 +4564,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128970450</v>
+        <v>128970440</v>
       </c>
       <c r="B42" t="n">
-        <v>92993</v>
+        <v>79619</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4575,21 +4575,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2079</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4599,10 +4599,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>730520</v>
+        <v>730523</v>
       </c>
       <c r="R42" t="n">
-        <v>7400447</v>
+        <v>7400413</v>
       </c>
       <c r="S42" t="n">
         <v>3</v>
@@ -4664,7 +4664,7 @@
         <v>128970442</v>
       </c>
       <c r="B43" t="n">
-        <v>79714</v>
+        <v>79619</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>128970448</v>
       </c>
       <c r="B44" t="n">
-        <v>92810</v>
+        <v>92815</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 44203-2025 artfynd.xlsx
+++ b/artfynd/A 44203-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128532926</v>
       </c>
       <c r="B2" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1266,32 +1266,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128944688</v>
+        <v>128944690</v>
       </c>
       <c r="B8" t="n">
-        <v>78791</v>
+        <v>91681</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730461</v>
+        <v>730508</v>
       </c>
       <c r="R8" t="n">
-        <v>7400442</v>
+        <v>7400458</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1363,7 +1363,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128944687</v>
+        <v>128944688</v>
       </c>
       <c r="B9" t="n">
         <v>78791</v>
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>730470</v>
+        <v>730461</v>
       </c>
       <c r="R9" t="n">
-        <v>7400373</v>
+        <v>7400442</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1460,32 +1460,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128944690</v>
+        <v>128944687</v>
       </c>
       <c r="B10" t="n">
-        <v>91681</v>
+        <v>78791</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>730508</v>
+        <v>730470</v>
       </c>
       <c r="R10" t="n">
-        <v>7400458</v>
+        <v>7400373</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1751,32 +1751,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128944691</v>
+        <v>128944686</v>
       </c>
       <c r="B13" t="n">
-        <v>92811</v>
+        <v>78791</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>730498</v>
+        <v>730518</v>
       </c>
       <c r="R13" t="n">
-        <v>7400295</v>
+        <v>7400367</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1848,32 +1848,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128944686</v>
+        <v>128944691</v>
       </c>
       <c r="B14" t="n">
-        <v>78791</v>
+        <v>92811</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>730518</v>
+        <v>730498</v>
       </c>
       <c r="R14" t="n">
-        <v>7400367</v>
+        <v>7400295</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2624,32 +2624,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128970462</v>
+        <v>128970454</v>
       </c>
       <c r="B22" t="n">
-        <v>92811</v>
+        <v>78791</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>730496</v>
+        <v>730523</v>
       </c>
       <c r="R22" t="n">
-        <v>7400291</v>
+        <v>7400319</v>
       </c>
       <c r="S22" t="n">
         <v>3</v>
@@ -2721,32 +2721,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128970454</v>
+        <v>128970462</v>
       </c>
       <c r="B23" t="n">
-        <v>78791</v>
+        <v>92811</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2756,10 +2756,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>730523</v>
+        <v>730496</v>
       </c>
       <c r="R23" t="n">
-        <v>7400319</v>
+        <v>7400291</v>
       </c>
       <c r="S23" t="n">
         <v>3</v>
@@ -4467,10 +4467,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128970440</v>
+        <v>128970450</v>
       </c>
       <c r="B41" t="n">
-        <v>79624</v>
+        <v>93006</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4478,21 +4478,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229821</v>
+        <v>2079</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4502,10 +4502,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>730523</v>
+        <v>730520</v>
       </c>
       <c r="R41" t="n">
-        <v>7400413</v>
+        <v>7400447</v>
       </c>
       <c r="S41" t="n">
         <v>3</v>
@@ -4564,10 +4564,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128970450</v>
+        <v>128970440</v>
       </c>
       <c r="B42" t="n">
-        <v>93006</v>
+        <v>79624</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4575,21 +4575,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2079</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4599,10 +4599,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>730520</v>
+        <v>730523</v>
       </c>
       <c r="R42" t="n">
-        <v>7400447</v>
+        <v>7400413</v>
       </c>
       <c r="S42" t="n">
         <v>3</v>

--- a/artfynd/A 44203-2025 artfynd.xlsx
+++ b/artfynd/A 44203-2025 artfynd.xlsx
@@ -1075,7 +1075,7 @@
         <v>128944692</v>
       </c>
       <c r="B6" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>128944690</v>
       </c>
       <c r="B8" t="n">
-        <v>91681</v>
+        <v>91684</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>128944674</v>
       </c>
       <c r="B12" t="n">
-        <v>90552</v>
+        <v>90555</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1751,32 +1751,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128944686</v>
+        <v>128944691</v>
       </c>
       <c r="B13" t="n">
-        <v>78791</v>
+        <v>92816</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>730518</v>
+        <v>730498</v>
       </c>
       <c r="R13" t="n">
-        <v>7400367</v>
+        <v>7400295</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1848,32 +1848,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128944691</v>
+        <v>128944686</v>
       </c>
       <c r="B14" t="n">
-        <v>92811</v>
+        <v>78791</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>730498</v>
+        <v>730518</v>
       </c>
       <c r="R14" t="n">
-        <v>7400295</v>
+        <v>7400367</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1948,7 +1948,7 @@
         <v>128944673</v>
       </c>
       <c r="B15" t="n">
-        <v>90552</v>
+        <v>90555</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         <v>128944678</v>
       </c>
       <c r="B17" t="n">
-        <v>92842</v>
+        <v>92847</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>128944693</v>
       </c>
       <c r="B19" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>128944672</v>
       </c>
       <c r="B21" t="n">
-        <v>91695</v>
+        <v>91698</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2624,32 +2624,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128970454</v>
+        <v>128970462</v>
       </c>
       <c r="B22" t="n">
-        <v>78791</v>
+        <v>92816</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>730523</v>
+        <v>730496</v>
       </c>
       <c r="R22" t="n">
-        <v>7400319</v>
+        <v>7400291</v>
       </c>
       <c r="S22" t="n">
         <v>3</v>
@@ -2721,32 +2721,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128970462</v>
+        <v>128970454</v>
       </c>
       <c r="B23" t="n">
-        <v>92811</v>
+        <v>78791</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2756,10 +2756,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>730496</v>
+        <v>730523</v>
       </c>
       <c r="R23" t="n">
-        <v>7400291</v>
+        <v>7400319</v>
       </c>
       <c r="S23" t="n">
         <v>3</v>
@@ -3015,7 +3015,7 @@
         <v>128970445</v>
       </c>
       <c r="B26" t="n">
-        <v>92815</v>
+        <v>92820</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>128970447</v>
       </c>
       <c r="B27" t="n">
-        <v>92823</v>
+        <v>92828</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>128970464</v>
       </c>
       <c r="B28" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3303,32 +3303,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128970461</v>
+        <v>128970443</v>
       </c>
       <c r="B29" t="n">
-        <v>92811</v>
+        <v>79624</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3338,10 +3338,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>730490</v>
+        <v>730506</v>
       </c>
       <c r="R29" t="n">
-        <v>7400286</v>
+        <v>7400283</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3400,32 +3400,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128970456</v>
+        <v>128970461</v>
       </c>
       <c r="B30" t="n">
-        <v>78791</v>
+        <v>92816</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3435,10 +3435,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>730514</v>
+        <v>730490</v>
       </c>
       <c r="R30" t="n">
-        <v>7400402</v>
+        <v>7400286</v>
       </c>
       <c r="S30" t="n">
         <v>3</v>
@@ -3497,32 +3497,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128970444</v>
+        <v>128970456</v>
       </c>
       <c r="B31" t="n">
-        <v>92795</v>
+        <v>78791</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6055</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3532,10 +3532,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>730530</v>
+        <v>730514</v>
       </c>
       <c r="R31" t="n">
-        <v>7400285</v>
+        <v>7400402</v>
       </c>
       <c r="S31" t="n">
         <v>3</v>
@@ -3594,32 +3594,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128970443</v>
+        <v>128970444</v>
       </c>
       <c r="B32" t="n">
-        <v>79624</v>
+        <v>92800</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>6055</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>730506</v>
+        <v>730530</v>
       </c>
       <c r="R32" t="n">
-        <v>7400283</v>
+        <v>7400285</v>
       </c>
       <c r="S32" t="n">
         <v>3</v>
@@ -3691,10 +3691,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128970460</v>
+        <v>128970453</v>
       </c>
       <c r="B33" t="n">
-        <v>79113</v>
+        <v>78792</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3702,21 +3702,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>864</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3726,10 +3726,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>730589</v>
+        <v>730495</v>
       </c>
       <c r="R33" t="n">
-        <v>7400431</v>
+        <v>7400399</v>
       </c>
       <c r="S33" t="n">
         <v>3</v>
@@ -3788,10 +3788,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128970453</v>
+        <v>128970460</v>
       </c>
       <c r="B34" t="n">
-        <v>78792</v>
+        <v>79113</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3799,21 +3799,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>864</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3823,10 +3823,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>730495</v>
+        <v>730589</v>
       </c>
       <c r="R34" t="n">
-        <v>7400399</v>
+        <v>7400431</v>
       </c>
       <c r="S34" t="n">
         <v>3</v>
@@ -3885,32 +3885,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128970449</v>
+        <v>128970457</v>
       </c>
       <c r="B35" t="n">
-        <v>97522</v>
+        <v>78791</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221945</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3920,10 +3920,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>730553</v>
+        <v>730492</v>
       </c>
       <c r="R35" t="n">
-        <v>7400437</v>
+        <v>7400398</v>
       </c>
       <c r="S35" t="n">
         <v>3</v>
@@ -3982,32 +3982,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128970457</v>
+        <v>128970449</v>
       </c>
       <c r="B36" t="n">
-        <v>78791</v>
+        <v>97527</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>221945</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4017,10 +4017,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>730492</v>
+        <v>730553</v>
       </c>
       <c r="R36" t="n">
-        <v>7400398</v>
+        <v>7400437</v>
       </c>
       <c r="S36" t="n">
         <v>3</v>
@@ -4079,32 +4079,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128970441</v>
+        <v>128970463</v>
       </c>
       <c r="B37" t="n">
-        <v>79624</v>
+        <v>92816</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4114,10 +4114,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>730604</v>
+        <v>730531</v>
       </c>
       <c r="R37" t="n">
-        <v>7400290</v>
+        <v>7400330</v>
       </c>
       <c r="S37" t="n">
         <v>3</v>
@@ -4273,32 +4273,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128970463</v>
+        <v>128970441</v>
       </c>
       <c r="B39" t="n">
-        <v>92811</v>
+        <v>79624</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4308,10 +4308,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>730531</v>
+        <v>730604</v>
       </c>
       <c r="R39" t="n">
-        <v>7400330</v>
+        <v>7400290</v>
       </c>
       <c r="S39" t="n">
         <v>3</v>
@@ -4470,7 +4470,7 @@
         <v>128970450</v>
       </c>
       <c r="B41" t="n">
-        <v>93006</v>
+        <v>93011</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>128970448</v>
       </c>
       <c r="B44" t="n">
-        <v>92823</v>
+        <v>92828</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 44203-2025 artfynd.xlsx
+++ b/artfynd/A 44203-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128532926</v>
       </c>
       <c r="B2" t="n">
-        <v>92823</v>
+        <v>92831</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128944684</v>
       </c>
       <c r="B3" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>128944682</v>
       </c>
       <c r="B4" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>128944689</v>
       </c>
       <c r="B5" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>128944692</v>
       </c>
       <c r="B6" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>128944683</v>
       </c>
       <c r="B7" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>128944690</v>
       </c>
       <c r="B8" t="n">
-        <v>91684</v>
+        <v>91687</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>128944688</v>
       </c>
       <c r="B9" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>128944687</v>
       </c>
       <c r="B10" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>128944680</v>
       </c>
       <c r="B11" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>128944674</v>
       </c>
       <c r="B12" t="n">
-        <v>90555</v>
+        <v>90558</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1751,32 +1751,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128944691</v>
+        <v>128944686</v>
       </c>
       <c r="B13" t="n">
-        <v>92816</v>
+        <v>78792</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>730498</v>
+        <v>730518</v>
       </c>
       <c r="R13" t="n">
-        <v>7400295</v>
+        <v>7400367</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1848,32 +1848,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128944686</v>
+        <v>128944691</v>
       </c>
       <c r="B14" t="n">
-        <v>78791</v>
+        <v>92819</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>730518</v>
+        <v>730498</v>
       </c>
       <c r="R14" t="n">
-        <v>7400367</v>
+        <v>7400295</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1945,32 +1945,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128944673</v>
+        <v>128944678</v>
       </c>
       <c r="B15" t="n">
-        <v>90555</v>
+        <v>92850</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1962</v>
+        <v>232140</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>730476</v>
+        <v>730462</v>
       </c>
       <c r="R15" t="n">
-        <v>7400283</v>
+        <v>7400313</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2042,10 +2042,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128944685</v>
+        <v>128944673</v>
       </c>
       <c r="B16" t="n">
-        <v>78791</v>
+        <v>90558</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2053,21 +2053,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>730663</v>
+        <v>730476</v>
       </c>
       <c r="R16" t="n">
-        <v>7400366</v>
+        <v>7400283</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2139,32 +2139,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128944678</v>
+        <v>128944685</v>
       </c>
       <c r="B17" t="n">
-        <v>92847</v>
+        <v>78792</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>232140</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2174,10 +2174,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>730462</v>
+        <v>730663</v>
       </c>
       <c r="R17" t="n">
-        <v>7400313</v>
+        <v>7400366</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2239,7 +2239,7 @@
         <v>128944679</v>
       </c>
       <c r="B18" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>128944693</v>
       </c>
       <c r="B19" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>128944681</v>
       </c>
       <c r="B20" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>128944672</v>
       </c>
       <c r="B21" t="n">
-        <v>91698</v>
+        <v>91701</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>128970462</v>
       </c>
       <c r="B22" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>128970454</v>
       </c>
       <c r="B23" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>128970459</v>
       </c>
       <c r="B24" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>128970458</v>
       </c>
       <c r="B25" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>128970445</v>
       </c>
       <c r="B26" t="n">
-        <v>92820</v>
+        <v>92823</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>128970447</v>
       </c>
       <c r="B27" t="n">
-        <v>92828</v>
+        <v>92831</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>128970464</v>
       </c>
       <c r="B28" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3303,32 +3303,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128970443</v>
+        <v>128970461</v>
       </c>
       <c r="B29" t="n">
-        <v>79624</v>
+        <v>92819</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3338,10 +3338,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>730506</v>
+        <v>730490</v>
       </c>
       <c r="R29" t="n">
-        <v>7400283</v>
+        <v>7400286</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3400,32 +3400,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128970461</v>
+        <v>128970444</v>
       </c>
       <c r="B30" t="n">
-        <v>92816</v>
+        <v>92803</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>6055</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3435,10 +3435,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>730490</v>
+        <v>730530</v>
       </c>
       <c r="R30" t="n">
-        <v>7400286</v>
+        <v>7400285</v>
       </c>
       <c r="S30" t="n">
         <v>3</v>
@@ -3500,7 +3500,7 @@
         <v>128970456</v>
       </c>
       <c r="B31" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3594,32 +3594,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128970444</v>
+        <v>128970443</v>
       </c>
       <c r="B32" t="n">
-        <v>92800</v>
+        <v>79625</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6055</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>730530</v>
+        <v>730506</v>
       </c>
       <c r="R32" t="n">
-        <v>7400285</v>
+        <v>7400283</v>
       </c>
       <c r="S32" t="n">
         <v>3</v>
@@ -3694,7 +3694,7 @@
         <v>128970453</v>
       </c>
       <c r="B33" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         <v>128970460</v>
       </c>
       <c r="B34" t="n">
-        <v>79113</v>
+        <v>79114</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3885,32 +3885,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128970457</v>
+        <v>128970449</v>
       </c>
       <c r="B35" t="n">
-        <v>78791</v>
+        <v>97530</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>221945</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3920,10 +3920,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>730492</v>
+        <v>730553</v>
       </c>
       <c r="R35" t="n">
-        <v>7400398</v>
+        <v>7400437</v>
       </c>
       <c r="S35" t="n">
         <v>3</v>
@@ -3982,32 +3982,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128970449</v>
+        <v>128970457</v>
       </c>
       <c r="B36" t="n">
-        <v>97527</v>
+        <v>78792</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221945</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4017,10 +4017,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>730553</v>
+        <v>730492</v>
       </c>
       <c r="R36" t="n">
-        <v>7400437</v>
+        <v>7400398</v>
       </c>
       <c r="S36" t="n">
         <v>3</v>
@@ -4082,7 +4082,7 @@
         <v>128970463</v>
       </c>
       <c r="B37" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4176,10 +4176,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128970452</v>
+        <v>128970441</v>
       </c>
       <c r="B38" t="n">
-        <v>78792</v>
+        <v>79625</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4187,21 +4187,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4211,10 +4211,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>730572</v>
+        <v>730604</v>
       </c>
       <c r="R38" t="n">
-        <v>7400289</v>
+        <v>7400290</v>
       </c>
       <c r="S38" t="n">
         <v>3</v>
@@ -4273,10 +4273,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128970441</v>
+        <v>128970452</v>
       </c>
       <c r="B39" t="n">
-        <v>79624</v>
+        <v>78793</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4284,21 +4284,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4308,10 +4308,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>730604</v>
+        <v>730572</v>
       </c>
       <c r="R39" t="n">
-        <v>7400290</v>
+        <v>7400289</v>
       </c>
       <c r="S39" t="n">
         <v>3</v>
@@ -4373,7 +4373,7 @@
         <v>128970455</v>
       </c>
       <c r="B40" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4467,10 +4467,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128970450</v>
+        <v>128970440</v>
       </c>
       <c r="B41" t="n">
-        <v>93011</v>
+        <v>79625</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4478,21 +4478,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2079</v>
+        <v>229821</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4502,10 +4502,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>730520</v>
+        <v>730523</v>
       </c>
       <c r="R41" t="n">
-        <v>7400447</v>
+        <v>7400413</v>
       </c>
       <c r="S41" t="n">
         <v>3</v>
@@ -4564,10 +4564,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128970440</v>
+        <v>128970450</v>
       </c>
       <c r="B42" t="n">
-        <v>79624</v>
+        <v>93014</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4575,21 +4575,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229821</v>
+        <v>2079</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4599,10 +4599,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>730523</v>
+        <v>730520</v>
       </c>
       <c r="R42" t="n">
-        <v>7400413</v>
+        <v>7400447</v>
       </c>
       <c r="S42" t="n">
         <v>3</v>
@@ -4664,7 +4664,7 @@
         <v>128970442</v>
       </c>
       <c r="B43" t="n">
-        <v>79624</v>
+        <v>79625</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>128970448</v>
       </c>
       <c r="B44" t="n">
-        <v>92828</v>
+        <v>92831</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 44203-2025 artfynd.xlsx
+++ b/artfynd/A 44203-2025 artfynd.xlsx
@@ -1654,10 +1654,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128944674</v>
+        <v>128944686</v>
       </c>
       <c r="B12" t="n">
-        <v>90558</v>
+        <v>78792</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1665,21 +1665,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>730365</v>
+        <v>730518</v>
       </c>
       <c r="R12" t="n">
-        <v>7400452</v>
+        <v>7400367</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1751,10 +1751,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128944686</v>
+        <v>128944674</v>
       </c>
       <c r="B13" t="n">
-        <v>78792</v>
+        <v>90558</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1762,21 +1762,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>730518</v>
+        <v>730365</v>
       </c>
       <c r="R13" t="n">
-        <v>7400367</v>
+        <v>7400452</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2624,32 +2624,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128970462</v>
+        <v>128970454</v>
       </c>
       <c r="B22" t="n">
-        <v>92819</v>
+        <v>78792</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>730496</v>
+        <v>730523</v>
       </c>
       <c r="R22" t="n">
-        <v>7400291</v>
+        <v>7400319</v>
       </c>
       <c r="S22" t="n">
         <v>3</v>
@@ -2721,32 +2721,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128970454</v>
+        <v>128970462</v>
       </c>
       <c r="B23" t="n">
-        <v>78792</v>
+        <v>92819</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2756,10 +2756,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>730523</v>
+        <v>730496</v>
       </c>
       <c r="R23" t="n">
-        <v>7400319</v>
+        <v>7400291</v>
       </c>
       <c r="S23" t="n">
         <v>3</v>
@@ -3885,32 +3885,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128970449</v>
+        <v>128970457</v>
       </c>
       <c r="B35" t="n">
-        <v>97530</v>
+        <v>78792</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221945</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3920,10 +3920,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>730553</v>
+        <v>730492</v>
       </c>
       <c r="R35" t="n">
-        <v>7400437</v>
+        <v>7400398</v>
       </c>
       <c r="S35" t="n">
         <v>3</v>
@@ -3982,32 +3982,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128970457</v>
+        <v>128970449</v>
       </c>
       <c r="B36" t="n">
-        <v>78792</v>
+        <v>97530</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>221945</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4017,10 +4017,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>730492</v>
+        <v>730553</v>
       </c>
       <c r="R36" t="n">
-        <v>7400398</v>
+        <v>7400437</v>
       </c>
       <c r="S36" t="n">
         <v>3</v>

--- a/artfynd/A 44203-2025 artfynd.xlsx
+++ b/artfynd/A 44203-2025 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128944684</v>
+        <v>128944682</v>
       </c>
       <c r="B3" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730648</v>
+        <v>730487</v>
       </c>
       <c r="R3" t="n">
-        <v>7400352</v>
+        <v>7400456</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -878,10 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128944682</v>
+        <v>128944684</v>
       </c>
       <c r="B4" t="n">
-        <v>78793</v>
+        <v>78792</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -889,21 +889,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730487</v>
+        <v>730648</v>
       </c>
       <c r="R4" t="n">
-        <v>7400456</v>
+        <v>7400352</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1266,32 +1266,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128944690</v>
+        <v>128944688</v>
       </c>
       <c r="B8" t="n">
-        <v>91687</v>
+        <v>78792</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730508</v>
+        <v>730461</v>
       </c>
       <c r="R8" t="n">
-        <v>7400458</v>
+        <v>7400442</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1363,7 +1363,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128944688</v>
+        <v>128944687</v>
       </c>
       <c r="B9" t="n">
         <v>78792</v>
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>730461</v>
+        <v>730470</v>
       </c>
       <c r="R9" t="n">
-        <v>7400442</v>
+        <v>7400373</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1460,32 +1460,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128944687</v>
+        <v>128944690</v>
       </c>
       <c r="B10" t="n">
-        <v>78792</v>
+        <v>91687</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>730470</v>
+        <v>730508</v>
       </c>
       <c r="R10" t="n">
-        <v>7400373</v>
+        <v>7400458</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -2624,32 +2624,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128970454</v>
+        <v>128970462</v>
       </c>
       <c r="B22" t="n">
-        <v>78792</v>
+        <v>92819</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>730523</v>
+        <v>730496</v>
       </c>
       <c r="R22" t="n">
-        <v>7400319</v>
+        <v>7400291</v>
       </c>
       <c r="S22" t="n">
         <v>3</v>
@@ -2721,32 +2721,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128970462</v>
+        <v>128970454</v>
       </c>
       <c r="B23" t="n">
-        <v>92819</v>
+        <v>78792</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2756,10 +2756,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>730496</v>
+        <v>730523</v>
       </c>
       <c r="R23" t="n">
-        <v>7400291</v>
+        <v>7400319</v>
       </c>
       <c r="S23" t="n">
         <v>3</v>

--- a/artfynd/A 44203-2025 artfynd.xlsx
+++ b/artfynd/A 44203-2025 artfynd.xlsx
@@ -1266,32 +1266,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128944688</v>
+        <v>128944690</v>
       </c>
       <c r="B8" t="n">
-        <v>78792</v>
+        <v>91687</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730461</v>
+        <v>730508</v>
       </c>
       <c r="R8" t="n">
-        <v>7400442</v>
+        <v>7400458</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1460,32 +1460,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128944690</v>
+        <v>128944688</v>
       </c>
       <c r="B10" t="n">
-        <v>91687</v>
+        <v>78792</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>730508</v>
+        <v>730461</v>
       </c>
       <c r="R10" t="n">
-        <v>7400458</v>
+        <v>7400442</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128944686</v>
+        <v>128944674</v>
       </c>
       <c r="B12" t="n">
-        <v>78792</v>
+        <v>90558</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1665,21 +1665,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>730518</v>
+        <v>730365</v>
       </c>
       <c r="R12" t="n">
-        <v>7400367</v>
+        <v>7400452</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1751,10 +1751,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128944674</v>
+        <v>128944686</v>
       </c>
       <c r="B13" t="n">
-        <v>90558</v>
+        <v>78792</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1762,21 +1762,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>730365</v>
+        <v>730518</v>
       </c>
       <c r="R13" t="n">
-        <v>7400452</v>
+        <v>7400367</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -3400,32 +3400,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128970444</v>
+        <v>128970456</v>
       </c>
       <c r="B30" t="n">
-        <v>92803</v>
+        <v>78792</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6055</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3435,10 +3435,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>730530</v>
+        <v>730514</v>
       </c>
       <c r="R30" t="n">
-        <v>7400285</v>
+        <v>7400402</v>
       </c>
       <c r="S30" t="n">
         <v>3</v>
@@ -3497,32 +3497,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128970456</v>
+        <v>128970444</v>
       </c>
       <c r="B31" t="n">
-        <v>78792</v>
+        <v>92803</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6055</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3532,10 +3532,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>730514</v>
+        <v>730530</v>
       </c>
       <c r="R31" t="n">
-        <v>7400402</v>
+        <v>7400285</v>
       </c>
       <c r="S31" t="n">
         <v>3</v>
@@ -3691,10 +3691,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128970453</v>
+        <v>128970460</v>
       </c>
       <c r="B33" t="n">
-        <v>78793</v>
+        <v>79114</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3702,21 +3702,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>864</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3726,10 +3726,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>730495</v>
+        <v>730589</v>
       </c>
       <c r="R33" t="n">
-        <v>7400399</v>
+        <v>7400431</v>
       </c>
       <c r="S33" t="n">
         <v>3</v>
@@ -3788,10 +3788,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128970460</v>
+        <v>128970453</v>
       </c>
       <c r="B34" t="n">
-        <v>79114</v>
+        <v>78793</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3799,21 +3799,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>864</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3823,10 +3823,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>730589</v>
+        <v>730495</v>
       </c>
       <c r="R34" t="n">
-        <v>7400431</v>
+        <v>7400399</v>
       </c>
       <c r="S34" t="n">
         <v>3</v>
@@ -4467,10 +4467,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128970440</v>
+        <v>128970450</v>
       </c>
       <c r="B41" t="n">
-        <v>79625</v>
+        <v>93014</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4478,21 +4478,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229821</v>
+        <v>2079</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4502,10 +4502,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>730523</v>
+        <v>730520</v>
       </c>
       <c r="R41" t="n">
-        <v>7400413</v>
+        <v>7400447</v>
       </c>
       <c r="S41" t="n">
         <v>3</v>
@@ -4564,10 +4564,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128970450</v>
+        <v>128970440</v>
       </c>
       <c r="B42" t="n">
-        <v>93014</v>
+        <v>79625</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4575,21 +4575,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2079</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4599,10 +4599,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>730520</v>
+        <v>730523</v>
       </c>
       <c r="R42" t="n">
-        <v>7400447</v>
+        <v>7400413</v>
       </c>
       <c r="S42" t="n">
         <v>3</v>

--- a/artfynd/A 44203-2025 artfynd.xlsx
+++ b/artfynd/A 44203-2025 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128944682</v>
+        <v>128944684</v>
       </c>
       <c r="B3" t="n">
-        <v>78793</v>
+        <v>78796</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730487</v>
+        <v>730648</v>
       </c>
       <c r="R3" t="n">
-        <v>7400456</v>
+        <v>7400352</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -878,10 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128944684</v>
+        <v>128944682</v>
       </c>
       <c r="B4" t="n">
-        <v>78792</v>
+        <v>78797</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -889,21 +889,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730648</v>
+        <v>730487</v>
       </c>
       <c r="R4" t="n">
-        <v>7400352</v>
+        <v>7400456</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -978,7 +978,7 @@
         <v>128944689</v>
       </c>
       <c r="B5" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>128944692</v>
       </c>
       <c r="B6" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>128944683</v>
       </c>
       <c r="B7" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>128944690</v>
       </c>
       <c r="B8" t="n">
-        <v>91687</v>
+        <v>91694</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,10 +1363,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128944687</v>
+        <v>128944688</v>
       </c>
       <c r="B9" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>730470</v>
+        <v>730461</v>
       </c>
       <c r="R9" t="n">
-        <v>7400373</v>
+        <v>7400442</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1460,10 +1460,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128944688</v>
+        <v>128944687</v>
       </c>
       <c r="B10" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>730461</v>
+        <v>730470</v>
       </c>
       <c r="R10" t="n">
-        <v>7400442</v>
+        <v>7400373</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1560,7 +1560,7 @@
         <v>128944680</v>
       </c>
       <c r="B11" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1654,32 +1654,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128944674</v>
+        <v>128944691</v>
       </c>
       <c r="B12" t="n">
-        <v>90558</v>
+        <v>92826</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>730365</v>
+        <v>730498</v>
       </c>
       <c r="R12" t="n">
-        <v>7400452</v>
+        <v>7400295</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1751,10 +1751,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128944686</v>
+        <v>128944674</v>
       </c>
       <c r="B13" t="n">
-        <v>78792</v>
+        <v>90562</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1762,21 +1762,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>730518</v>
+        <v>730365</v>
       </c>
       <c r="R13" t="n">
-        <v>7400367</v>
+        <v>7400452</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1848,32 +1848,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128944691</v>
+        <v>128944686</v>
       </c>
       <c r="B14" t="n">
-        <v>92819</v>
+        <v>78796</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>730498</v>
+        <v>730518</v>
       </c>
       <c r="R14" t="n">
-        <v>7400295</v>
+        <v>7400367</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1945,32 +1945,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128944678</v>
+        <v>128944685</v>
       </c>
       <c r="B15" t="n">
-        <v>92850</v>
+        <v>78796</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>232140</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>730462</v>
+        <v>730663</v>
       </c>
       <c r="R15" t="n">
-        <v>7400313</v>
+        <v>7400366</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2042,32 +2042,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128944673</v>
+        <v>128944678</v>
       </c>
       <c r="B16" t="n">
-        <v>90558</v>
+        <v>92857</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1962</v>
+        <v>232140</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>730476</v>
+        <v>730462</v>
       </c>
       <c r="R16" t="n">
-        <v>7400283</v>
+        <v>7400313</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2139,10 +2139,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128944685</v>
+        <v>128944673</v>
       </c>
       <c r="B17" t="n">
-        <v>78792</v>
+        <v>90562</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2150,21 +2150,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2174,10 +2174,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>730663</v>
+        <v>730476</v>
       </c>
       <c r="R17" t="n">
-        <v>7400366</v>
+        <v>7400283</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2239,7 +2239,7 @@
         <v>128944679</v>
       </c>
       <c r="B18" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>128944693</v>
       </c>
       <c r="B19" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>128944681</v>
       </c>
       <c r="B20" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>128944672</v>
       </c>
       <c r="B21" t="n">
-        <v>91701</v>
+        <v>91708</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>128970462</v>
       </c>
       <c r="B22" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>128970454</v>
       </c>
       <c r="B23" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>128970459</v>
       </c>
       <c r="B24" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>128970458</v>
       </c>
       <c r="B25" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>128970445</v>
       </c>
       <c r="B26" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>128970447</v>
       </c>
       <c r="B27" t="n">
-        <v>92831</v>
+        <v>92838</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>128970464</v>
       </c>
       <c r="B28" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3303,32 +3303,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128970461</v>
+        <v>128970443</v>
       </c>
       <c r="B29" t="n">
-        <v>92819</v>
+        <v>79629</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3338,10 +3338,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>730490</v>
+        <v>730506</v>
       </c>
       <c r="R29" t="n">
-        <v>7400286</v>
+        <v>7400283</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3400,32 +3400,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128970456</v>
+        <v>128970461</v>
       </c>
       <c r="B30" t="n">
-        <v>78792</v>
+        <v>92826</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3435,10 +3435,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>730514</v>
+        <v>730490</v>
       </c>
       <c r="R30" t="n">
-        <v>7400402</v>
+        <v>7400286</v>
       </c>
       <c r="S30" t="n">
         <v>3</v>
@@ -3497,32 +3497,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128970444</v>
+        <v>128970456</v>
       </c>
       <c r="B31" t="n">
-        <v>92803</v>
+        <v>78796</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6055</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3532,10 +3532,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>730530</v>
+        <v>730514</v>
       </c>
       <c r="R31" t="n">
-        <v>7400285</v>
+        <v>7400402</v>
       </c>
       <c r="S31" t="n">
         <v>3</v>
@@ -3594,32 +3594,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128970443</v>
+        <v>128970444</v>
       </c>
       <c r="B32" t="n">
-        <v>79625</v>
+        <v>92810</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>6055</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>730506</v>
+        <v>730530</v>
       </c>
       <c r="R32" t="n">
-        <v>7400283</v>
+        <v>7400285</v>
       </c>
       <c r="S32" t="n">
         <v>3</v>
@@ -3691,10 +3691,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128970460</v>
+        <v>128970453</v>
       </c>
       <c r="B33" t="n">
-        <v>79114</v>
+        <v>78797</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3702,21 +3702,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>864</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3726,10 +3726,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>730589</v>
+        <v>730495</v>
       </c>
       <c r="R33" t="n">
-        <v>7400431</v>
+        <v>7400399</v>
       </c>
       <c r="S33" t="n">
         <v>3</v>
@@ -3788,10 +3788,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128970453</v>
+        <v>128970460</v>
       </c>
       <c r="B34" t="n">
-        <v>78793</v>
+        <v>79118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3799,21 +3799,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>864</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3823,10 +3823,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>730495</v>
+        <v>730589</v>
       </c>
       <c r="R34" t="n">
-        <v>7400399</v>
+        <v>7400431</v>
       </c>
       <c r="S34" t="n">
         <v>3</v>
@@ -3888,7 +3888,7 @@
         <v>128970457</v>
       </c>
       <c r="B35" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>128970449</v>
       </c>
       <c r="B36" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         <v>128970463</v>
       </c>
       <c r="B37" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4176,10 +4176,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128970441</v>
+        <v>128970452</v>
       </c>
       <c r="B38" t="n">
-        <v>79625</v>
+        <v>78797</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4187,21 +4187,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4211,10 +4211,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>730604</v>
+        <v>730572</v>
       </c>
       <c r="R38" t="n">
-        <v>7400290</v>
+        <v>7400289</v>
       </c>
       <c r="S38" t="n">
         <v>3</v>
@@ -4273,10 +4273,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128970452</v>
+        <v>128970441</v>
       </c>
       <c r="B39" t="n">
-        <v>78793</v>
+        <v>79629</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4284,21 +4284,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4308,10 +4308,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>730572</v>
+        <v>730604</v>
       </c>
       <c r="R39" t="n">
-        <v>7400289</v>
+        <v>7400290</v>
       </c>
       <c r="S39" t="n">
         <v>3</v>
@@ -4373,7 +4373,7 @@
         <v>128970455</v>
       </c>
       <c r="B40" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>128970450</v>
       </c>
       <c r="B41" t="n">
-        <v>93014</v>
+        <v>93022</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>128970440</v>
       </c>
       <c r="B42" t="n">
-        <v>79625</v>
+        <v>79629</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>128970442</v>
       </c>
       <c r="B43" t="n">
-        <v>79625</v>
+        <v>79629</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>128970448</v>
       </c>
       <c r="B44" t="n">
-        <v>92831</v>
+        <v>92838</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 44203-2025 artfynd.xlsx
+++ b/artfynd/A 44203-2025 artfynd.xlsx
@@ -3303,32 +3303,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128970443</v>
+        <v>128970444</v>
       </c>
       <c r="B29" t="n">
-        <v>79629</v>
+        <v>92810</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229821</v>
+        <v>6055</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3338,10 +3338,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>730506</v>
+        <v>730530</v>
       </c>
       <c r="R29" t="n">
-        <v>7400283</v>
+        <v>7400285</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3400,32 +3400,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128970461</v>
+        <v>128970443</v>
       </c>
       <c r="B30" t="n">
-        <v>92826</v>
+        <v>79629</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3435,10 +3435,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>730490</v>
+        <v>730506</v>
       </c>
       <c r="R30" t="n">
-        <v>7400286</v>
+        <v>7400283</v>
       </c>
       <c r="S30" t="n">
         <v>3</v>
@@ -3497,32 +3497,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128970456</v>
+        <v>128970461</v>
       </c>
       <c r="B31" t="n">
-        <v>78796</v>
+        <v>92826</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3532,10 +3532,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>730514</v>
+        <v>730490</v>
       </c>
       <c r="R31" t="n">
-        <v>7400402</v>
+        <v>7400286</v>
       </c>
       <c r="S31" t="n">
         <v>3</v>
@@ -3594,32 +3594,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128970444</v>
+        <v>128970456</v>
       </c>
       <c r="B32" t="n">
-        <v>92810</v>
+        <v>78796</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6055</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>730530</v>
+        <v>730514</v>
       </c>
       <c r="R32" t="n">
-        <v>7400285</v>
+        <v>7400402</v>
       </c>
       <c r="S32" t="n">
         <v>3</v>

--- a/artfynd/A 44203-2025 artfynd.xlsx
+++ b/artfynd/A 44203-2025 artfynd.xlsx
@@ -1075,7 +1075,7 @@
         <v>128944692</v>
       </c>
       <c r="B6" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1266,32 +1266,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128944690</v>
+        <v>128944688</v>
       </c>
       <c r="B8" t="n">
-        <v>91694</v>
+        <v>78796</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730508</v>
+        <v>730461</v>
       </c>
       <c r="R8" t="n">
-        <v>7400458</v>
+        <v>7400442</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1363,7 +1363,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128944688</v>
+        <v>128944687</v>
       </c>
       <c r="B9" t="n">
         <v>78796</v>
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>730461</v>
+        <v>730470</v>
       </c>
       <c r="R9" t="n">
-        <v>7400442</v>
+        <v>7400373</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1460,32 +1460,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128944687</v>
+        <v>128944690</v>
       </c>
       <c r="B10" t="n">
-        <v>78796</v>
+        <v>91701</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>730470</v>
+        <v>730508</v>
       </c>
       <c r="R10" t="n">
-        <v>7400373</v>
+        <v>7400458</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1654,32 +1654,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128944691</v>
+        <v>128944674</v>
       </c>
       <c r="B12" t="n">
-        <v>92826</v>
+        <v>90569</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>730498</v>
+        <v>730365</v>
       </c>
       <c r="R12" t="n">
-        <v>7400295</v>
+        <v>7400452</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1751,10 +1751,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128944674</v>
+        <v>128944686</v>
       </c>
       <c r="B13" t="n">
-        <v>90562</v>
+        <v>78796</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1762,21 +1762,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>730365</v>
+        <v>730518</v>
       </c>
       <c r="R13" t="n">
-        <v>7400452</v>
+        <v>7400367</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1848,32 +1848,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128944686</v>
+        <v>128944691</v>
       </c>
       <c r="B14" t="n">
-        <v>78796</v>
+        <v>92833</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>730518</v>
+        <v>730498</v>
       </c>
       <c r="R14" t="n">
-        <v>7400367</v>
+        <v>7400295</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1945,10 +1945,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128944685</v>
+        <v>128944673</v>
       </c>
       <c r="B15" t="n">
-        <v>78796</v>
+        <v>90569</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1956,21 +1956,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>730663</v>
+        <v>730476</v>
       </c>
       <c r="R15" t="n">
-        <v>7400366</v>
+        <v>7400283</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2042,32 +2042,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128944678</v>
+        <v>128944685</v>
       </c>
       <c r="B16" t="n">
-        <v>92857</v>
+        <v>78796</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>232140</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>730462</v>
+        <v>730663</v>
       </c>
       <c r="R16" t="n">
-        <v>7400313</v>
+        <v>7400366</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2139,32 +2139,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128944673</v>
+        <v>128944678</v>
       </c>
       <c r="B17" t="n">
-        <v>90562</v>
+        <v>92864</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1962</v>
+        <v>232140</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2174,10 +2174,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>730476</v>
+        <v>730462</v>
       </c>
       <c r="R17" t="n">
-        <v>7400283</v>
+        <v>7400313</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2336,7 +2336,7 @@
         <v>128944693</v>
       </c>
       <c r="B19" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>128944672</v>
       </c>
       <c r="B21" t="n">
-        <v>91708</v>
+        <v>91715</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>128970462</v>
       </c>
       <c r="B22" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>128970445</v>
       </c>
       <c r="B26" t="n">
-        <v>92830</v>
+        <v>92837</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>128970447</v>
       </c>
       <c r="B27" t="n">
-        <v>92838</v>
+        <v>92845</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>128970464</v>
       </c>
       <c r="B28" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3303,32 +3303,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128970444</v>
+        <v>128970443</v>
       </c>
       <c r="B29" t="n">
-        <v>92810</v>
+        <v>79629</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6055</v>
+        <v>229821</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3338,10 +3338,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>730530</v>
+        <v>730506</v>
       </c>
       <c r="R29" t="n">
-        <v>7400285</v>
+        <v>7400283</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3400,32 +3400,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128970443</v>
+        <v>128970461</v>
       </c>
       <c r="B30" t="n">
-        <v>79629</v>
+        <v>92833</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3435,10 +3435,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>730506</v>
+        <v>730490</v>
       </c>
       <c r="R30" t="n">
-        <v>7400283</v>
+        <v>7400286</v>
       </c>
       <c r="S30" t="n">
         <v>3</v>
@@ -3497,32 +3497,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128970461</v>
+        <v>128970444</v>
       </c>
       <c r="B31" t="n">
-        <v>92826</v>
+        <v>92817</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>6055</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3532,10 +3532,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>730490</v>
+        <v>730530</v>
       </c>
       <c r="R31" t="n">
-        <v>7400286</v>
+        <v>7400285</v>
       </c>
       <c r="S31" t="n">
         <v>3</v>
@@ -3885,32 +3885,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128970457</v>
+        <v>128970449</v>
       </c>
       <c r="B35" t="n">
-        <v>78796</v>
+        <v>97547</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>221945</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3920,10 +3920,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>730492</v>
+        <v>730553</v>
       </c>
       <c r="R35" t="n">
-        <v>7400398</v>
+        <v>7400437</v>
       </c>
       <c r="S35" t="n">
         <v>3</v>
@@ -3982,32 +3982,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128970449</v>
+        <v>128970457</v>
       </c>
       <c r="B36" t="n">
-        <v>97540</v>
+        <v>78796</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221945</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4017,10 +4017,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>730553</v>
+        <v>730492</v>
       </c>
       <c r="R36" t="n">
-        <v>7400437</v>
+        <v>7400398</v>
       </c>
       <c r="S36" t="n">
         <v>3</v>
@@ -4082,7 +4082,7 @@
         <v>128970463</v>
       </c>
       <c r="B37" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4176,10 +4176,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128970452</v>
+        <v>128970441</v>
       </c>
       <c r="B38" t="n">
-        <v>78797</v>
+        <v>79629</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4187,21 +4187,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4211,10 +4211,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>730572</v>
+        <v>730604</v>
       </c>
       <c r="R38" t="n">
-        <v>7400289</v>
+        <v>7400290</v>
       </c>
       <c r="S38" t="n">
         <v>3</v>
@@ -4273,10 +4273,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128970441</v>
+        <v>128970452</v>
       </c>
       <c r="B39" t="n">
-        <v>79629</v>
+        <v>78797</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4284,21 +4284,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4308,10 +4308,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>730604</v>
+        <v>730572</v>
       </c>
       <c r="R39" t="n">
-        <v>7400290</v>
+        <v>7400289</v>
       </c>
       <c r="S39" t="n">
         <v>3</v>
@@ -4470,7 +4470,7 @@
         <v>128970450</v>
       </c>
       <c r="B41" t="n">
-        <v>93022</v>
+        <v>93029</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>128970448</v>
       </c>
       <c r="B44" t="n">
-        <v>92838</v>
+        <v>92845</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 44203-2025 artfynd.xlsx
+++ b/artfynd/A 44203-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>128944684</v>
       </c>
       <c r="B3" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>128944682</v>
       </c>
       <c r="B4" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>128944689</v>
       </c>
       <c r="B5" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>128944692</v>
       </c>
       <c r="B6" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>128944683</v>
       </c>
       <c r="B7" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>128944688</v>
       </c>
       <c r="B8" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>128944687</v>
       </c>
       <c r="B9" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>128944690</v>
       </c>
       <c r="B10" t="n">
-        <v>91701</v>
+        <v>91703</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>128944680</v>
       </c>
       <c r="B11" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1654,32 +1654,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128944674</v>
+        <v>128944691</v>
       </c>
       <c r="B12" t="n">
-        <v>90569</v>
+        <v>92835</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>730365</v>
+        <v>730498</v>
       </c>
       <c r="R12" t="n">
-        <v>7400452</v>
+        <v>7400295</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1751,10 +1751,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128944686</v>
+        <v>128944674</v>
       </c>
       <c r="B13" t="n">
-        <v>78796</v>
+        <v>90571</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1762,21 +1762,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>730518</v>
+        <v>730365</v>
       </c>
       <c r="R13" t="n">
-        <v>7400367</v>
+        <v>7400452</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1848,32 +1848,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128944691</v>
+        <v>128944686</v>
       </c>
       <c r="B14" t="n">
-        <v>92833</v>
+        <v>78798</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>730498</v>
+        <v>730518</v>
       </c>
       <c r="R14" t="n">
-        <v>7400295</v>
+        <v>7400367</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1948,7 +1948,7 @@
         <v>128944673</v>
       </c>
       <c r="B15" t="n">
-        <v>90569</v>
+        <v>90571</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>128944685</v>
       </c>
       <c r="B16" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         <v>128944678</v>
       </c>
       <c r="B17" t="n">
-        <v>92864</v>
+        <v>92866</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>128944679</v>
       </c>
       <c r="B18" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2333,32 +2333,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128944693</v>
+        <v>128944681</v>
       </c>
       <c r="B19" t="n">
-        <v>92833</v>
+        <v>78799</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2368,10 +2368,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>730500</v>
+        <v>730491</v>
       </c>
       <c r="R19" t="n">
-        <v>7400421</v>
+        <v>7400393</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2430,32 +2430,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128944681</v>
+        <v>128944693</v>
       </c>
       <c r="B20" t="n">
-        <v>78797</v>
+        <v>92835</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>730491</v>
+        <v>730500</v>
       </c>
       <c r="R20" t="n">
-        <v>7400393</v>
+        <v>7400421</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2530,7 +2530,7 @@
         <v>128944672</v>
       </c>
       <c r="B21" t="n">
-        <v>91715</v>
+        <v>91717</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>128970462</v>
       </c>
       <c r="B22" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>128970454</v>
       </c>
       <c r="B23" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>128970459</v>
       </c>
       <c r="B24" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>128970458</v>
       </c>
       <c r="B25" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>128970445</v>
       </c>
       <c r="B26" t="n">
-        <v>92837</v>
+        <v>92839</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>128970447</v>
       </c>
       <c r="B27" t="n">
-        <v>92845</v>
+        <v>92847</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>128970464</v>
       </c>
       <c r="B28" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3303,32 +3303,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128970443</v>
+        <v>128970461</v>
       </c>
       <c r="B29" t="n">
-        <v>79629</v>
+        <v>92835</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3338,10 +3338,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>730506</v>
+        <v>730490</v>
       </c>
       <c r="R29" t="n">
-        <v>7400283</v>
+        <v>7400286</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3400,32 +3400,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128970461</v>
+        <v>128970444</v>
       </c>
       <c r="B30" t="n">
-        <v>92833</v>
+        <v>92819</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>6055</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3435,10 +3435,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>730490</v>
+        <v>730530</v>
       </c>
       <c r="R30" t="n">
-        <v>7400286</v>
+        <v>7400285</v>
       </c>
       <c r="S30" t="n">
         <v>3</v>
@@ -3497,32 +3497,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128970444</v>
+        <v>128970456</v>
       </c>
       <c r="B31" t="n">
-        <v>92817</v>
+        <v>78798</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6055</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3532,10 +3532,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>730530</v>
+        <v>730514</v>
       </c>
       <c r="R31" t="n">
-        <v>7400285</v>
+        <v>7400402</v>
       </c>
       <c r="S31" t="n">
         <v>3</v>
@@ -3594,10 +3594,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128970456</v>
+        <v>128970443</v>
       </c>
       <c r="B32" t="n">
-        <v>78796</v>
+        <v>79631</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3605,21 +3605,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>730514</v>
+        <v>730506</v>
       </c>
       <c r="R32" t="n">
-        <v>7400402</v>
+        <v>7400283</v>
       </c>
       <c r="S32" t="n">
         <v>3</v>
@@ -3691,10 +3691,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128970453</v>
+        <v>128970460</v>
       </c>
       <c r="B33" t="n">
-        <v>78797</v>
+        <v>79120</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3702,21 +3702,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>864</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3726,10 +3726,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>730495</v>
+        <v>730589</v>
       </c>
       <c r="R33" t="n">
-        <v>7400399</v>
+        <v>7400431</v>
       </c>
       <c r="S33" t="n">
         <v>3</v>
@@ -3788,10 +3788,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128970460</v>
+        <v>128970453</v>
       </c>
       <c r="B34" t="n">
-        <v>79118</v>
+        <v>78799</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3799,21 +3799,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>864</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3823,10 +3823,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>730589</v>
+        <v>730495</v>
       </c>
       <c r="R34" t="n">
-        <v>7400431</v>
+        <v>7400399</v>
       </c>
       <c r="S34" t="n">
         <v>3</v>
@@ -3885,32 +3885,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128970449</v>
+        <v>128970457</v>
       </c>
       <c r="B35" t="n">
-        <v>97547</v>
+        <v>78798</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221945</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3920,10 +3920,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>730553</v>
+        <v>730492</v>
       </c>
       <c r="R35" t="n">
-        <v>7400437</v>
+        <v>7400398</v>
       </c>
       <c r="S35" t="n">
         <v>3</v>
@@ -3982,32 +3982,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128970457</v>
+        <v>128970449</v>
       </c>
       <c r="B36" t="n">
-        <v>78796</v>
+        <v>97549</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>221945</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4017,10 +4017,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>730492</v>
+        <v>730553</v>
       </c>
       <c r="R36" t="n">
-        <v>7400398</v>
+        <v>7400437</v>
       </c>
       <c r="S36" t="n">
         <v>3</v>
@@ -4079,32 +4079,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128970463</v>
+        <v>128970452</v>
       </c>
       <c r="B37" t="n">
-        <v>92833</v>
+        <v>78799</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4114,10 +4114,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>730531</v>
+        <v>730572</v>
       </c>
       <c r="R37" t="n">
-        <v>7400330</v>
+        <v>7400289</v>
       </c>
       <c r="S37" t="n">
         <v>3</v>
@@ -4176,32 +4176,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128970441</v>
+        <v>128970463</v>
       </c>
       <c r="B38" t="n">
-        <v>79629</v>
+        <v>92835</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4211,10 +4211,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>730604</v>
+        <v>730531</v>
       </c>
       <c r="R38" t="n">
-        <v>7400290</v>
+        <v>7400330</v>
       </c>
       <c r="S38" t="n">
         <v>3</v>
@@ -4273,10 +4273,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128970452</v>
+        <v>128970441</v>
       </c>
       <c r="B39" t="n">
-        <v>78797</v>
+        <v>79631</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4284,21 +4284,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4308,10 +4308,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>730572</v>
+        <v>730604</v>
       </c>
       <c r="R39" t="n">
-        <v>7400289</v>
+        <v>7400290</v>
       </c>
       <c r="S39" t="n">
         <v>3</v>
@@ -4373,7 +4373,7 @@
         <v>128970455</v>
       </c>
       <c r="B40" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>128970450</v>
       </c>
       <c r="B41" t="n">
-        <v>93029</v>
+        <v>93031</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>128970440</v>
       </c>
       <c r="B42" t="n">
-        <v>79629</v>
+        <v>79631</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>128970442</v>
       </c>
       <c r="B43" t="n">
-        <v>79629</v>
+        <v>79631</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>128970448</v>
       </c>
       <c r="B44" t="n">
-        <v>92845</v>
+        <v>92847</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 44203-2025 artfynd.xlsx
+++ b/artfynd/A 44203-2025 artfynd.xlsx
@@ -1654,32 +1654,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128944691</v>
+        <v>128944674</v>
       </c>
       <c r="B12" t="n">
-        <v>92835</v>
+        <v>90571</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>730498</v>
+        <v>730365</v>
       </c>
       <c r="R12" t="n">
-        <v>7400295</v>
+        <v>7400452</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1751,32 +1751,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128944674</v>
+        <v>128944691</v>
       </c>
       <c r="B13" t="n">
-        <v>90571</v>
+        <v>92835</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>730365</v>
+        <v>730498</v>
       </c>
       <c r="R13" t="n">
-        <v>7400452</v>
+        <v>7400295</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1945,10 +1945,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128944673</v>
+        <v>128944685</v>
       </c>
       <c r="B15" t="n">
-        <v>90571</v>
+        <v>78798</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1956,21 +1956,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>730476</v>
+        <v>730663</v>
       </c>
       <c r="R15" t="n">
-        <v>7400283</v>
+        <v>7400366</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2042,10 +2042,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128944685</v>
+        <v>128944673</v>
       </c>
       <c r="B16" t="n">
-        <v>78798</v>
+        <v>90571</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2053,21 +2053,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>730663</v>
+        <v>730476</v>
       </c>
       <c r="R16" t="n">
-        <v>7400366</v>
+        <v>7400283</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2333,32 +2333,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128944681</v>
+        <v>128944693</v>
       </c>
       <c r="B19" t="n">
-        <v>78799</v>
+        <v>92835</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2368,10 +2368,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>730491</v>
+        <v>730500</v>
       </c>
       <c r="R19" t="n">
-        <v>7400393</v>
+        <v>7400421</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2430,32 +2430,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128944693</v>
+        <v>128944681</v>
       </c>
       <c r="B20" t="n">
-        <v>92835</v>
+        <v>78799</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>730500</v>
+        <v>730491</v>
       </c>
       <c r="R20" t="n">
-        <v>7400421</v>
+        <v>7400393</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3400,32 +3400,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128970444</v>
+        <v>128970456</v>
       </c>
       <c r="B30" t="n">
-        <v>92819</v>
+        <v>78798</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6055</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3435,10 +3435,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>730530</v>
+        <v>730514</v>
       </c>
       <c r="R30" t="n">
-        <v>7400285</v>
+        <v>7400402</v>
       </c>
       <c r="S30" t="n">
         <v>3</v>
@@ -3497,32 +3497,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128970456</v>
+        <v>128970444</v>
       </c>
       <c r="B31" t="n">
-        <v>78798</v>
+        <v>92819</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6055</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3532,10 +3532,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>730514</v>
+        <v>730530</v>
       </c>
       <c r="R31" t="n">
-        <v>7400402</v>
+        <v>7400285</v>
       </c>
       <c r="S31" t="n">
         <v>3</v>
@@ -4079,10 +4079,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128970452</v>
+        <v>128970441</v>
       </c>
       <c r="B37" t="n">
-        <v>78799</v>
+        <v>79631</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4090,21 +4090,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4114,10 +4114,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>730572</v>
+        <v>730604</v>
       </c>
       <c r="R37" t="n">
-        <v>7400289</v>
+        <v>7400290</v>
       </c>
       <c r="S37" t="n">
         <v>3</v>
@@ -4176,32 +4176,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128970463</v>
+        <v>128970452</v>
       </c>
       <c r="B38" t="n">
-        <v>92835</v>
+        <v>78799</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4211,10 +4211,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>730531</v>
+        <v>730572</v>
       </c>
       <c r="R38" t="n">
-        <v>7400330</v>
+        <v>7400289</v>
       </c>
       <c r="S38" t="n">
         <v>3</v>
@@ -4273,32 +4273,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128970441</v>
+        <v>128970463</v>
       </c>
       <c r="B39" t="n">
-        <v>79631</v>
+        <v>92835</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4308,10 +4308,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>730604</v>
+        <v>730531</v>
       </c>
       <c r="R39" t="n">
-        <v>7400290</v>
+        <v>7400330</v>
       </c>
       <c r="S39" t="n">
         <v>3</v>

--- a/artfynd/A 44203-2025 artfynd.xlsx
+++ b/artfynd/A 44203-2025 artfynd.xlsx
@@ -2042,32 +2042,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128944673</v>
+        <v>128944678</v>
       </c>
       <c r="B16" t="n">
-        <v>90571</v>
+        <v>92866</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1962</v>
+        <v>232140</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>730476</v>
+        <v>730462</v>
       </c>
       <c r="R16" t="n">
-        <v>7400283</v>
+        <v>7400313</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2139,32 +2139,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128944678</v>
+        <v>128944673</v>
       </c>
       <c r="B17" t="n">
-        <v>92866</v>
+        <v>90571</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>232140</v>
+        <v>1962</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2174,10 +2174,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>730462</v>
+        <v>730476</v>
       </c>
       <c r="R17" t="n">
-        <v>7400313</v>
+        <v>7400283</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -3303,32 +3303,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128970461</v>
+        <v>128970444</v>
       </c>
       <c r="B29" t="n">
-        <v>92835</v>
+        <v>92819</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>6055</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3338,10 +3338,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>730490</v>
+        <v>730530</v>
       </c>
       <c r="R29" t="n">
-        <v>7400286</v>
+        <v>7400285</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3400,32 +3400,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128970456</v>
+        <v>128970461</v>
       </c>
       <c r="B30" t="n">
-        <v>78798</v>
+        <v>92835</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3435,10 +3435,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>730514</v>
+        <v>730490</v>
       </c>
       <c r="R30" t="n">
-        <v>7400402</v>
+        <v>7400286</v>
       </c>
       <c r="S30" t="n">
         <v>3</v>
@@ -3497,32 +3497,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128970444</v>
+        <v>128970456</v>
       </c>
       <c r="B31" t="n">
-        <v>92819</v>
+        <v>78798</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6055</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3532,10 +3532,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>730530</v>
+        <v>730514</v>
       </c>
       <c r="R31" t="n">
-        <v>7400285</v>
+        <v>7400402</v>
       </c>
       <c r="S31" t="n">
         <v>3</v>
@@ -4079,32 +4079,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128970441</v>
+        <v>128970463</v>
       </c>
       <c r="B37" t="n">
-        <v>79631</v>
+        <v>92835</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4114,10 +4114,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>730604</v>
+        <v>730531</v>
       </c>
       <c r="R37" t="n">
-        <v>7400290</v>
+        <v>7400330</v>
       </c>
       <c r="S37" t="n">
         <v>3</v>
@@ -4176,10 +4176,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128970452</v>
+        <v>128970441</v>
       </c>
       <c r="B38" t="n">
-        <v>78799</v>
+        <v>79631</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4187,21 +4187,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4211,10 +4211,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>730572</v>
+        <v>730604</v>
       </c>
       <c r="R38" t="n">
-        <v>7400289</v>
+        <v>7400290</v>
       </c>
       <c r="S38" t="n">
         <v>3</v>
@@ -4273,32 +4273,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128970463</v>
+        <v>128970452</v>
       </c>
       <c r="B39" t="n">
-        <v>92835</v>
+        <v>78799</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4308,10 +4308,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>730531</v>
+        <v>730572</v>
       </c>
       <c r="R39" t="n">
-        <v>7400330</v>
+        <v>7400289</v>
       </c>
       <c r="S39" t="n">
         <v>3</v>
@@ -4467,10 +4467,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128970450</v>
+        <v>128970440</v>
       </c>
       <c r="B41" t="n">
-        <v>93031</v>
+        <v>79631</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4478,21 +4478,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2079</v>
+        <v>229821</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4502,10 +4502,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>730520</v>
+        <v>730523</v>
       </c>
       <c r="R41" t="n">
-        <v>7400447</v>
+        <v>7400413</v>
       </c>
       <c r="S41" t="n">
         <v>3</v>
@@ -4564,10 +4564,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128970440</v>
+        <v>128970450</v>
       </c>
       <c r="B42" t="n">
-        <v>79631</v>
+        <v>93031</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4575,21 +4575,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229821</v>
+        <v>2079</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4599,10 +4599,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>730523</v>
+        <v>730520</v>
       </c>
       <c r="R42" t="n">
-        <v>7400413</v>
+        <v>7400447</v>
       </c>
       <c r="S42" t="n">
         <v>3</v>

--- a/artfynd/A 44203-2025 artfynd.xlsx
+++ b/artfynd/A 44203-2025 artfynd.xlsx
@@ -1075,7 +1075,7 @@
         <v>128944692</v>
       </c>
       <c r="B6" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>128944690</v>
       </c>
       <c r="B10" t="n">
-        <v>91703</v>
+        <v>91712</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128944674</v>
+        <v>128944686</v>
       </c>
       <c r="B12" t="n">
-        <v>90571</v>
+        <v>78798</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1665,21 +1665,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>730365</v>
+        <v>730518</v>
       </c>
       <c r="R12" t="n">
-        <v>7400452</v>
+        <v>7400367</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1754,7 +1754,7 @@
         <v>128944691</v>
       </c>
       <c r="B13" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1848,10 +1848,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128944686</v>
+        <v>128944674</v>
       </c>
       <c r="B14" t="n">
-        <v>78798</v>
+        <v>90572</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1859,21 +1859,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>730518</v>
+        <v>730365</v>
       </c>
       <c r="R14" t="n">
-        <v>7400367</v>
+        <v>7400452</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1945,10 +1945,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128944685</v>
+        <v>128944673</v>
       </c>
       <c r="B15" t="n">
-        <v>78798</v>
+        <v>90572</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1956,21 +1956,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>730663</v>
+        <v>730476</v>
       </c>
       <c r="R15" t="n">
-        <v>7400366</v>
+        <v>7400283</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2042,32 +2042,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128944678</v>
+        <v>128944685</v>
       </c>
       <c r="B16" t="n">
-        <v>92866</v>
+        <v>78798</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>232140</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>730462</v>
+        <v>730663</v>
       </c>
       <c r="R16" t="n">
-        <v>7400313</v>
+        <v>7400366</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2139,32 +2139,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128944673</v>
+        <v>128944678</v>
       </c>
       <c r="B17" t="n">
-        <v>90571</v>
+        <v>92852</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1962</v>
+        <v>232140</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2174,10 +2174,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>730476</v>
+        <v>730462</v>
       </c>
       <c r="R17" t="n">
-        <v>7400283</v>
+        <v>7400313</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2336,7 +2336,7 @@
         <v>128944693</v>
       </c>
       <c r="B19" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>128944672</v>
       </c>
       <c r="B21" t="n">
-        <v>91717</v>
+        <v>91726</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>128970462</v>
       </c>
       <c r="B22" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>128970445</v>
       </c>
       <c r="B26" t="n">
-        <v>92839</v>
+        <v>92825</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>128970447</v>
       </c>
       <c r="B27" t="n">
-        <v>92847</v>
+        <v>92833</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>128970464</v>
       </c>
       <c r="B28" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3303,32 +3303,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128970444</v>
+        <v>128970456</v>
       </c>
       <c r="B29" t="n">
-        <v>92819</v>
+        <v>78798</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6055</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3338,10 +3338,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>730530</v>
+        <v>730514</v>
       </c>
       <c r="R29" t="n">
-        <v>7400285</v>
+        <v>7400402</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3400,32 +3400,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128970461</v>
+        <v>128970444</v>
       </c>
       <c r="B30" t="n">
-        <v>92835</v>
+        <v>92805</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>6055</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3435,10 +3435,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>730490</v>
+        <v>730530</v>
       </c>
       <c r="R30" t="n">
-        <v>7400286</v>
+        <v>7400285</v>
       </c>
       <c r="S30" t="n">
         <v>3</v>
@@ -3497,10 +3497,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128970456</v>
+        <v>128970443</v>
       </c>
       <c r="B31" t="n">
-        <v>78798</v>
+        <v>79631</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3508,21 +3508,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3532,10 +3532,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>730514</v>
+        <v>730506</v>
       </c>
       <c r="R31" t="n">
-        <v>7400402</v>
+        <v>7400283</v>
       </c>
       <c r="S31" t="n">
         <v>3</v>
@@ -3594,32 +3594,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128970443</v>
+        <v>128970461</v>
       </c>
       <c r="B32" t="n">
-        <v>79631</v>
+        <v>92821</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>730506</v>
+        <v>730490</v>
       </c>
       <c r="R32" t="n">
-        <v>7400283</v>
+        <v>7400286</v>
       </c>
       <c r="S32" t="n">
         <v>3</v>
@@ -3985,7 +3985,7 @@
         <v>128970449</v>
       </c>
       <c r="B36" t="n">
-        <v>97549</v>
+        <v>97575</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         <v>128970463</v>
       </c>
       <c r="B37" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4467,10 +4467,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128970440</v>
+        <v>128970450</v>
       </c>
       <c r="B41" t="n">
-        <v>79631</v>
+        <v>91592</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4478,21 +4478,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229821</v>
+        <v>2079</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4502,10 +4502,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>730523</v>
+        <v>730520</v>
       </c>
       <c r="R41" t="n">
-        <v>7400413</v>
+        <v>7400447</v>
       </c>
       <c r="S41" t="n">
         <v>3</v>
@@ -4564,10 +4564,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128970450</v>
+        <v>128970440</v>
       </c>
       <c r="B42" t="n">
-        <v>93031</v>
+        <v>79631</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4575,21 +4575,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2079</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4599,10 +4599,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>730520</v>
+        <v>730523</v>
       </c>
       <c r="R42" t="n">
-        <v>7400447</v>
+        <v>7400413</v>
       </c>
       <c r="S42" t="n">
         <v>3</v>
@@ -4761,7 +4761,7 @@
         <v>128970448</v>
       </c>
       <c r="B44" t="n">
-        <v>92847</v>
+        <v>92833</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 44203-2025 artfynd.xlsx
+++ b/artfynd/A 44203-2025 artfynd.xlsx
@@ -1075,7 +1075,7 @@
         <v>128944692</v>
       </c>
       <c r="B6" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1266,32 +1266,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128944688</v>
+        <v>128944690</v>
       </c>
       <c r="B8" t="n">
-        <v>78798</v>
+        <v>91713</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730461</v>
+        <v>730508</v>
       </c>
       <c r="R8" t="n">
-        <v>7400442</v>
+        <v>7400458</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1363,7 +1363,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128944687</v>
+        <v>128944688</v>
       </c>
       <c r="B9" t="n">
         <v>78798</v>
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>730470</v>
+        <v>730461</v>
       </c>
       <c r="R9" t="n">
-        <v>7400373</v>
+        <v>7400442</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1460,32 +1460,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128944690</v>
+        <v>128944687</v>
       </c>
       <c r="B10" t="n">
-        <v>91712</v>
+        <v>78798</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>730508</v>
+        <v>730470</v>
       </c>
       <c r="R10" t="n">
-        <v>7400458</v>
+        <v>7400373</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128944686</v>
+        <v>128944674</v>
       </c>
       <c r="B12" t="n">
-        <v>78798</v>
+        <v>90572</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1665,21 +1665,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>730518</v>
+        <v>730365</v>
       </c>
       <c r="R12" t="n">
-        <v>7400367</v>
+        <v>7400452</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1751,32 +1751,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128944691</v>
+        <v>128944686</v>
       </c>
       <c r="B13" t="n">
-        <v>92821</v>
+        <v>78798</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>730498</v>
+        <v>730518</v>
       </c>
       <c r="R13" t="n">
-        <v>7400295</v>
+        <v>7400367</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1848,32 +1848,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128944674</v>
+        <v>128944691</v>
       </c>
       <c r="B14" t="n">
-        <v>90572</v>
+        <v>92822</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>730365</v>
+        <v>730498</v>
       </c>
       <c r="R14" t="n">
-        <v>7400452</v>
+        <v>7400295</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2142,7 +2142,7 @@
         <v>128944678</v>
       </c>
       <c r="B17" t="n">
-        <v>92852</v>
+        <v>92853</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>128944693</v>
       </c>
       <c r="B19" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>128944672</v>
       </c>
       <c r="B21" t="n">
-        <v>91726</v>
+        <v>91727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2624,32 +2624,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128970462</v>
+        <v>128970454</v>
       </c>
       <c r="B22" t="n">
-        <v>92821</v>
+        <v>78798</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>730496</v>
+        <v>730523</v>
       </c>
       <c r="R22" t="n">
-        <v>7400291</v>
+        <v>7400319</v>
       </c>
       <c r="S22" t="n">
         <v>3</v>
@@ -2721,32 +2721,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128970454</v>
+        <v>128970462</v>
       </c>
       <c r="B23" t="n">
-        <v>78798</v>
+        <v>92822</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2756,10 +2756,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>730523</v>
+        <v>730496</v>
       </c>
       <c r="R23" t="n">
-        <v>7400319</v>
+        <v>7400291</v>
       </c>
       <c r="S23" t="n">
         <v>3</v>
@@ -3012,32 +3012,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128970445</v>
+        <v>128970447</v>
       </c>
       <c r="B26" t="n">
-        <v>92825</v>
+        <v>92834</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4365</v>
+        <v>4366</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>730387</v>
+        <v>730515</v>
       </c>
       <c r="R26" t="n">
-        <v>7400491</v>
+        <v>7400280</v>
       </c>
       <c r="S26" t="n">
         <v>3</v>
@@ -3109,32 +3109,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128970447</v>
+        <v>128970445</v>
       </c>
       <c r="B27" t="n">
-        <v>92833</v>
+        <v>92826</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4366</v>
+        <v>4365</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3144,10 +3144,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>730515</v>
+        <v>730387</v>
       </c>
       <c r="R27" t="n">
-        <v>7400280</v>
+        <v>7400491</v>
       </c>
       <c r="S27" t="n">
         <v>3</v>
@@ -3209,7 +3209,7 @@
         <v>128970464</v>
       </c>
       <c r="B28" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3303,32 +3303,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128970456</v>
+        <v>128970461</v>
       </c>
       <c r="B29" t="n">
-        <v>78798</v>
+        <v>92822</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3338,10 +3338,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>730514</v>
+        <v>730490</v>
       </c>
       <c r="R29" t="n">
-        <v>7400402</v>
+        <v>7400286</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3400,32 +3400,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128970444</v>
+        <v>128970456</v>
       </c>
       <c r="B30" t="n">
-        <v>92805</v>
+        <v>78798</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6055</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3435,10 +3435,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>730530</v>
+        <v>730514</v>
       </c>
       <c r="R30" t="n">
-        <v>7400285</v>
+        <v>7400402</v>
       </c>
       <c r="S30" t="n">
         <v>3</v>
@@ -3497,32 +3497,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128970443</v>
+        <v>128970444</v>
       </c>
       <c r="B31" t="n">
-        <v>79631</v>
+        <v>92806</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229821</v>
+        <v>6055</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3532,10 +3532,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>730506</v>
+        <v>730530</v>
       </c>
       <c r="R31" t="n">
-        <v>7400283</v>
+        <v>7400285</v>
       </c>
       <c r="S31" t="n">
         <v>3</v>
@@ -3594,32 +3594,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128970461</v>
+        <v>128970443</v>
       </c>
       <c r="B32" t="n">
-        <v>92821</v>
+        <v>79631</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>730490</v>
+        <v>730506</v>
       </c>
       <c r="R32" t="n">
-        <v>7400286</v>
+        <v>7400283</v>
       </c>
       <c r="S32" t="n">
         <v>3</v>
@@ -3985,7 +3985,7 @@
         <v>128970449</v>
       </c>
       <c r="B36" t="n">
-        <v>97575</v>
+        <v>97576</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         <v>128970463</v>
       </c>
       <c r="B37" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4176,10 +4176,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128970441</v>
+        <v>128970452</v>
       </c>
       <c r="B38" t="n">
-        <v>79631</v>
+        <v>78799</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4187,21 +4187,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4211,10 +4211,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>730604</v>
+        <v>730572</v>
       </c>
       <c r="R38" t="n">
-        <v>7400290</v>
+        <v>7400289</v>
       </c>
       <c r="S38" t="n">
         <v>3</v>
@@ -4273,10 +4273,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128970452</v>
+        <v>128970441</v>
       </c>
       <c r="B39" t="n">
-        <v>78799</v>
+        <v>79631</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4284,21 +4284,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4308,10 +4308,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>730572</v>
+        <v>730604</v>
       </c>
       <c r="R39" t="n">
-        <v>7400289</v>
+        <v>7400290</v>
       </c>
       <c r="S39" t="n">
         <v>3</v>
@@ -4467,10 +4467,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128970450</v>
+        <v>128970440</v>
       </c>
       <c r="B41" t="n">
-        <v>91592</v>
+        <v>79631</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4478,21 +4478,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2079</v>
+        <v>229821</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4502,10 +4502,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>730520</v>
+        <v>730523</v>
       </c>
       <c r="R41" t="n">
-        <v>7400447</v>
+        <v>7400413</v>
       </c>
       <c r="S41" t="n">
         <v>3</v>
@@ -4564,10 +4564,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128970440</v>
+        <v>128970450</v>
       </c>
       <c r="B42" t="n">
-        <v>79631</v>
+        <v>91593</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4575,21 +4575,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229821</v>
+        <v>2079</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4599,10 +4599,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>730523</v>
+        <v>730520</v>
       </c>
       <c r="R42" t="n">
-        <v>7400413</v>
+        <v>7400447</v>
       </c>
       <c r="S42" t="n">
         <v>3</v>
@@ -4761,7 +4761,7 @@
         <v>128970448</v>
       </c>
       <c r="B44" t="n">
-        <v>92833</v>
+        <v>92834</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 44203-2025 artfynd.xlsx
+++ b/artfynd/A 44203-2025 artfynd.xlsx
@@ -1266,32 +1266,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128944690</v>
+        <v>128944688</v>
       </c>
       <c r="B8" t="n">
-        <v>91713</v>
+        <v>78798</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730508</v>
+        <v>730461</v>
       </c>
       <c r="R8" t="n">
-        <v>7400458</v>
+        <v>7400442</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1363,7 +1363,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128944688</v>
+        <v>128944687</v>
       </c>
       <c r="B9" t="n">
         <v>78798</v>
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>730461</v>
+        <v>730470</v>
       </c>
       <c r="R9" t="n">
-        <v>7400442</v>
+        <v>7400373</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1460,32 +1460,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128944687</v>
+        <v>128944690</v>
       </c>
       <c r="B10" t="n">
-        <v>78798</v>
+        <v>91713</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>730470</v>
+        <v>730508</v>
       </c>
       <c r="R10" t="n">
-        <v>7400373</v>
+        <v>7400458</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1654,32 +1654,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128944674</v>
+        <v>128944691</v>
       </c>
       <c r="B12" t="n">
-        <v>90572</v>
+        <v>92822</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>730365</v>
+        <v>730498</v>
       </c>
       <c r="R12" t="n">
-        <v>7400452</v>
+        <v>7400295</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1848,32 +1848,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128944691</v>
+        <v>128944674</v>
       </c>
       <c r="B14" t="n">
-        <v>92822</v>
+        <v>90572</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>730498</v>
+        <v>730365</v>
       </c>
       <c r="R14" t="n">
-        <v>7400295</v>
+        <v>7400452</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2042,32 +2042,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128944685</v>
+        <v>128944678</v>
       </c>
       <c r="B16" t="n">
-        <v>78798</v>
+        <v>92853</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>232140</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>730663</v>
+        <v>730462</v>
       </c>
       <c r="R16" t="n">
-        <v>7400366</v>
+        <v>7400313</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2139,32 +2139,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128944678</v>
+        <v>128944685</v>
       </c>
       <c r="B17" t="n">
-        <v>92853</v>
+        <v>78798</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>232140</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2174,10 +2174,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>730462</v>
+        <v>730663</v>
       </c>
       <c r="R17" t="n">
-        <v>7400313</v>
+        <v>7400366</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2333,32 +2333,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128944693</v>
+        <v>128944681</v>
       </c>
       <c r="B19" t="n">
-        <v>92822</v>
+        <v>78799</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2368,10 +2368,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>730500</v>
+        <v>730491</v>
       </c>
       <c r="R19" t="n">
-        <v>7400421</v>
+        <v>7400393</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2430,32 +2430,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128944681</v>
+        <v>128944693</v>
       </c>
       <c r="B20" t="n">
-        <v>78799</v>
+        <v>92822</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>730491</v>
+        <v>730500</v>
       </c>
       <c r="R20" t="n">
-        <v>7400393</v>
+        <v>7400421</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3012,32 +3012,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128970447</v>
+        <v>128970445</v>
       </c>
       <c r="B26" t="n">
-        <v>92834</v>
+        <v>92826</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4366</v>
+        <v>4365</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>730515</v>
+        <v>730387</v>
       </c>
       <c r="R26" t="n">
-        <v>7400280</v>
+        <v>7400491</v>
       </c>
       <c r="S26" t="n">
         <v>3</v>
@@ -3109,32 +3109,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128970445</v>
+        <v>128970447</v>
       </c>
       <c r="B27" t="n">
-        <v>92826</v>
+        <v>92834</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4365</v>
+        <v>4366</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3144,10 +3144,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>730387</v>
+        <v>730515</v>
       </c>
       <c r="R27" t="n">
-        <v>7400491</v>
+        <v>7400280</v>
       </c>
       <c r="S27" t="n">
         <v>3</v>
@@ -3303,32 +3303,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128970461</v>
+        <v>128970443</v>
       </c>
       <c r="B29" t="n">
-        <v>92822</v>
+        <v>79631</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3338,10 +3338,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>730490</v>
+        <v>730506</v>
       </c>
       <c r="R29" t="n">
-        <v>7400286</v>
+        <v>7400283</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3400,32 +3400,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128970456</v>
+        <v>128970461</v>
       </c>
       <c r="B30" t="n">
-        <v>78798</v>
+        <v>92822</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3435,10 +3435,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>730514</v>
+        <v>730490</v>
       </c>
       <c r="R30" t="n">
-        <v>7400402</v>
+        <v>7400286</v>
       </c>
       <c r="S30" t="n">
         <v>3</v>
@@ -3497,32 +3497,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128970444</v>
+        <v>128970456</v>
       </c>
       <c r="B31" t="n">
-        <v>92806</v>
+        <v>78798</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6055</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3532,10 +3532,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>730530</v>
+        <v>730514</v>
       </c>
       <c r="R31" t="n">
-        <v>7400285</v>
+        <v>7400402</v>
       </c>
       <c r="S31" t="n">
         <v>3</v>
@@ -3594,32 +3594,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128970443</v>
+        <v>128970444</v>
       </c>
       <c r="B32" t="n">
-        <v>79631</v>
+        <v>92806</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>6055</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>730506</v>
+        <v>730530</v>
       </c>
       <c r="R32" t="n">
-        <v>7400283</v>
+        <v>7400285</v>
       </c>
       <c r="S32" t="n">
         <v>3</v>
@@ -3985,7 +3985,7 @@
         <v>128970449</v>
       </c>
       <c r="B36" t="n">
-        <v>97576</v>
+        <v>97577</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4079,32 +4079,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128970463</v>
+        <v>128970441</v>
       </c>
       <c r="B37" t="n">
-        <v>92822</v>
+        <v>79631</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4114,10 +4114,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>730531</v>
+        <v>730604</v>
       </c>
       <c r="R37" t="n">
-        <v>7400330</v>
+        <v>7400290</v>
       </c>
       <c r="S37" t="n">
         <v>3</v>
@@ -4273,32 +4273,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128970441</v>
+        <v>128970463</v>
       </c>
       <c r="B39" t="n">
-        <v>79631</v>
+        <v>92822</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4308,10 +4308,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>730604</v>
+        <v>730531</v>
       </c>
       <c r="R39" t="n">
-        <v>7400290</v>
+        <v>7400330</v>
       </c>
       <c r="S39" t="n">
         <v>3</v>
@@ -4467,10 +4467,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128970440</v>
+        <v>128970450</v>
       </c>
       <c r="B41" t="n">
-        <v>79631</v>
+        <v>91593</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4478,21 +4478,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229821</v>
+        <v>2079</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4502,10 +4502,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>730523</v>
+        <v>730520</v>
       </c>
       <c r="R41" t="n">
-        <v>7400413</v>
+        <v>7400447</v>
       </c>
       <c r="S41" t="n">
         <v>3</v>
@@ -4564,10 +4564,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128970450</v>
+        <v>128970440</v>
       </c>
       <c r="B42" t="n">
-        <v>91593</v>
+        <v>79631</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4575,21 +4575,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2079</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4599,10 +4599,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>730520</v>
+        <v>730523</v>
       </c>
       <c r="R42" t="n">
-        <v>7400447</v>
+        <v>7400413</v>
       </c>
       <c r="S42" t="n">
         <v>3</v>

--- a/artfynd/A 44203-2025 artfynd.xlsx
+++ b/artfynd/A 44203-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>128944684</v>
       </c>
       <c r="B3" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>128944682</v>
       </c>
       <c r="B4" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>128944689</v>
       </c>
       <c r="B5" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>128944692</v>
       </c>
       <c r="B6" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>128944683</v>
       </c>
       <c r="B7" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1266,10 +1266,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128944688</v>
+        <v>128944687</v>
       </c>
       <c r="B8" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730461</v>
+        <v>730470</v>
       </c>
       <c r="R8" t="n">
-        <v>7400442</v>
+        <v>7400373</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1363,10 +1363,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128944687</v>
+        <v>128944688</v>
       </c>
       <c r="B9" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>730470</v>
+        <v>730461</v>
       </c>
       <c r="R9" t="n">
-        <v>7400373</v>
+        <v>7400442</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1463,7 +1463,7 @@
         <v>128944690</v>
       </c>
       <c r="B10" t="n">
-        <v>91713</v>
+        <v>91716</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>128944680</v>
       </c>
       <c r="B11" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>128944691</v>
       </c>
       <c r="B12" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>128944686</v>
       </c>
       <c r="B13" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>128944674</v>
       </c>
       <c r="B14" t="n">
-        <v>90572</v>
+        <v>90575</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>128944673</v>
       </c>
       <c r="B15" t="n">
-        <v>90572</v>
+        <v>90575</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2042,32 +2042,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128944678</v>
+        <v>128944685</v>
       </c>
       <c r="B16" t="n">
-        <v>92853</v>
+        <v>78800</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>232140</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>730462</v>
+        <v>730663</v>
       </c>
       <c r="R16" t="n">
-        <v>7400313</v>
+        <v>7400366</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2139,32 +2139,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128944685</v>
+        <v>128944678</v>
       </c>
       <c r="B17" t="n">
-        <v>78798</v>
+        <v>92856</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>232140</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2174,10 +2174,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>730663</v>
+        <v>730462</v>
       </c>
       <c r="R17" t="n">
-        <v>7400366</v>
+        <v>7400313</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2239,7 +2239,7 @@
         <v>128944679</v>
       </c>
       <c r="B18" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2333,32 +2333,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128944681</v>
+        <v>128944693</v>
       </c>
       <c r="B19" t="n">
-        <v>78799</v>
+        <v>92825</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2368,10 +2368,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>730491</v>
+        <v>730500</v>
       </c>
       <c r="R19" t="n">
-        <v>7400393</v>
+        <v>7400421</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2430,32 +2430,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128944693</v>
+        <v>128944681</v>
       </c>
       <c r="B20" t="n">
-        <v>92822</v>
+        <v>78801</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>730500</v>
+        <v>730491</v>
       </c>
       <c r="R20" t="n">
-        <v>7400421</v>
+        <v>7400393</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2530,7 +2530,7 @@
         <v>128944672</v>
       </c>
       <c r="B21" t="n">
-        <v>91727</v>
+        <v>91730</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2624,32 +2624,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128970454</v>
+        <v>128970462</v>
       </c>
       <c r="B22" t="n">
-        <v>78798</v>
+        <v>92825</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>730523</v>
+        <v>730496</v>
       </c>
       <c r="R22" t="n">
-        <v>7400319</v>
+        <v>7400291</v>
       </c>
       <c r="S22" t="n">
         <v>3</v>
@@ -2721,32 +2721,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128970462</v>
+        <v>128970454</v>
       </c>
       <c r="B23" t="n">
-        <v>92822</v>
+        <v>78800</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2756,10 +2756,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>730496</v>
+        <v>730523</v>
       </c>
       <c r="R23" t="n">
-        <v>7400291</v>
+        <v>7400319</v>
       </c>
       <c r="S23" t="n">
         <v>3</v>
@@ -2821,7 +2821,7 @@
         <v>128970459</v>
       </c>
       <c r="B24" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>128970458</v>
       </c>
       <c r="B25" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3012,32 +3012,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128970445</v>
+        <v>128970447</v>
       </c>
       <c r="B26" t="n">
-        <v>92826</v>
+        <v>92837</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4365</v>
+        <v>4366</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>730387</v>
+        <v>730515</v>
       </c>
       <c r="R26" t="n">
-        <v>7400491</v>
+        <v>7400280</v>
       </c>
       <c r="S26" t="n">
         <v>3</v>
@@ -3109,32 +3109,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128970447</v>
+        <v>128970445</v>
       </c>
       <c r="B27" t="n">
-        <v>92834</v>
+        <v>92829</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4366</v>
+        <v>4365</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3144,10 +3144,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>730515</v>
+        <v>730387</v>
       </c>
       <c r="R27" t="n">
-        <v>7400280</v>
+        <v>7400491</v>
       </c>
       <c r="S27" t="n">
         <v>3</v>
@@ -3209,7 +3209,7 @@
         <v>128970464</v>
       </c>
       <c r="B28" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3303,32 +3303,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128970443</v>
+        <v>128970461</v>
       </c>
       <c r="B29" t="n">
-        <v>79631</v>
+        <v>92825</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3338,10 +3338,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>730506</v>
+        <v>730490</v>
       </c>
       <c r="R29" t="n">
-        <v>7400283</v>
+        <v>7400286</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3400,32 +3400,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128970461</v>
+        <v>128970444</v>
       </c>
       <c r="B30" t="n">
-        <v>92822</v>
+        <v>92809</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>6055</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3435,10 +3435,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>730490</v>
+        <v>730530</v>
       </c>
       <c r="R30" t="n">
-        <v>7400286</v>
+        <v>7400285</v>
       </c>
       <c r="S30" t="n">
         <v>3</v>
@@ -3500,7 +3500,7 @@
         <v>128970456</v>
       </c>
       <c r="B31" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3594,32 +3594,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128970444</v>
+        <v>128970443</v>
       </c>
       <c r="B32" t="n">
-        <v>92806</v>
+        <v>79633</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6055</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>730530</v>
+        <v>730506</v>
       </c>
       <c r="R32" t="n">
-        <v>7400285</v>
+        <v>7400283</v>
       </c>
       <c r="S32" t="n">
         <v>3</v>
@@ -3694,7 +3694,7 @@
         <v>128970460</v>
       </c>
       <c r="B33" t="n">
-        <v>79120</v>
+        <v>79122</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         <v>128970453</v>
       </c>
       <c r="B34" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>128970457</v>
       </c>
       <c r="B35" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>128970449</v>
       </c>
       <c r="B36" t="n">
-        <v>97577</v>
+        <v>97581</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4079,32 +4079,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128970441</v>
+        <v>128970463</v>
       </c>
       <c r="B37" t="n">
-        <v>79631</v>
+        <v>92825</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4114,10 +4114,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>730604</v>
+        <v>730531</v>
       </c>
       <c r="R37" t="n">
-        <v>7400290</v>
+        <v>7400330</v>
       </c>
       <c r="S37" t="n">
         <v>3</v>
@@ -4176,10 +4176,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128970452</v>
+        <v>128970441</v>
       </c>
       <c r="B38" t="n">
-        <v>78799</v>
+        <v>79633</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4187,21 +4187,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4211,10 +4211,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>730572</v>
+        <v>730604</v>
       </c>
       <c r="R38" t="n">
-        <v>7400289</v>
+        <v>7400290</v>
       </c>
       <c r="S38" t="n">
         <v>3</v>
@@ -4273,32 +4273,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128970463</v>
+        <v>128970452</v>
       </c>
       <c r="B39" t="n">
-        <v>92822</v>
+        <v>78801</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4308,10 +4308,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>730531</v>
+        <v>730572</v>
       </c>
       <c r="R39" t="n">
-        <v>7400330</v>
+        <v>7400289</v>
       </c>
       <c r="S39" t="n">
         <v>3</v>
@@ -4373,7 +4373,7 @@
         <v>128970455</v>
       </c>
       <c r="B40" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>128970450</v>
       </c>
       <c r="B41" t="n">
-        <v>91593</v>
+        <v>91596</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>128970440</v>
       </c>
       <c r="B42" t="n">
-        <v>79631</v>
+        <v>79633</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>128970442</v>
       </c>
       <c r="B43" t="n">
-        <v>79631</v>
+        <v>79633</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>128970448</v>
       </c>
       <c r="B44" t="n">
-        <v>92834</v>
+        <v>92837</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 44203-2025 artfynd.xlsx
+++ b/artfynd/A 44203-2025 artfynd.xlsx
@@ -1945,32 +1945,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128944673</v>
+        <v>128944678</v>
       </c>
       <c r="B15" t="n">
-        <v>90575</v>
+        <v>92856</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1962</v>
+        <v>232140</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>730476</v>
+        <v>730462</v>
       </c>
       <c r="R15" t="n">
-        <v>7400283</v>
+        <v>7400313</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2042,10 +2042,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128944685</v>
+        <v>128944673</v>
       </c>
       <c r="B16" t="n">
-        <v>78800</v>
+        <v>90575</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2053,21 +2053,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>730663</v>
+        <v>730476</v>
       </c>
       <c r="R16" t="n">
-        <v>7400366</v>
+        <v>7400283</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2139,32 +2139,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128944678</v>
+        <v>128944685</v>
       </c>
       <c r="B17" t="n">
-        <v>92856</v>
+        <v>78800</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>232140</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2174,10 +2174,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>730462</v>
+        <v>730663</v>
       </c>
       <c r="R17" t="n">
-        <v>7400313</v>
+        <v>7400366</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -3303,32 +3303,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128970461</v>
+        <v>128970444</v>
       </c>
       <c r="B29" t="n">
-        <v>92825</v>
+        <v>92809</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>6055</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3338,10 +3338,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>730490</v>
+        <v>730530</v>
       </c>
       <c r="R29" t="n">
-        <v>7400286</v>
+        <v>7400285</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3400,32 +3400,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128970444</v>
+        <v>128970443</v>
       </c>
       <c r="B30" t="n">
-        <v>92809</v>
+        <v>79633</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6055</v>
+        <v>229821</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3435,10 +3435,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>730530</v>
+        <v>730506</v>
       </c>
       <c r="R30" t="n">
-        <v>7400285</v>
+        <v>7400283</v>
       </c>
       <c r="S30" t="n">
         <v>3</v>
@@ -3497,32 +3497,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128970456</v>
+        <v>128970461</v>
       </c>
       <c r="B31" t="n">
-        <v>78800</v>
+        <v>92825</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3532,10 +3532,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>730514</v>
+        <v>730490</v>
       </c>
       <c r="R31" t="n">
-        <v>7400402</v>
+        <v>7400286</v>
       </c>
       <c r="S31" t="n">
         <v>3</v>
@@ -3594,10 +3594,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128970443</v>
+        <v>128970456</v>
       </c>
       <c r="B32" t="n">
-        <v>79633</v>
+        <v>78800</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3605,21 +3605,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>730506</v>
+        <v>730514</v>
       </c>
       <c r="R32" t="n">
-        <v>7400283</v>
+        <v>7400402</v>
       </c>
       <c r="S32" t="n">
         <v>3</v>

--- a/artfynd/A 44203-2025 artfynd.xlsx
+++ b/artfynd/A 44203-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>128944684</v>
       </c>
       <c r="B3" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>128944682</v>
       </c>
       <c r="B4" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>128944689</v>
       </c>
       <c r="B5" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>128944692</v>
       </c>
       <c r="B6" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>128944683</v>
       </c>
       <c r="B7" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1266,32 +1266,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128944687</v>
+        <v>128944690</v>
       </c>
       <c r="B8" t="n">
-        <v>78800</v>
+        <v>91718</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730470</v>
+        <v>730508</v>
       </c>
       <c r="R8" t="n">
-        <v>7400373</v>
+        <v>7400458</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1366,7 +1366,7 @@
         <v>128944688</v>
       </c>
       <c r="B9" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1460,32 +1460,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128944690</v>
+        <v>128944687</v>
       </c>
       <c r="B10" t="n">
-        <v>91716</v>
+        <v>78801</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>730508</v>
+        <v>730470</v>
       </c>
       <c r="R10" t="n">
-        <v>7400458</v>
+        <v>7400373</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1560,7 +1560,7 @@
         <v>128944680</v>
       </c>
       <c r="B11" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1654,32 +1654,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128944691</v>
+        <v>128944686</v>
       </c>
       <c r="B12" t="n">
-        <v>92825</v>
+        <v>78801</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>730498</v>
+        <v>730518</v>
       </c>
       <c r="R12" t="n">
-        <v>7400295</v>
+        <v>7400367</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1751,10 +1751,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128944686</v>
+        <v>128944674</v>
       </c>
       <c r="B13" t="n">
-        <v>78800</v>
+        <v>90577</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1762,21 +1762,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>730518</v>
+        <v>730365</v>
       </c>
       <c r="R13" t="n">
-        <v>7400367</v>
+        <v>7400452</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1848,32 +1848,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128944674</v>
+        <v>128944691</v>
       </c>
       <c r="B14" t="n">
-        <v>90575</v>
+        <v>92827</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>730365</v>
+        <v>730498</v>
       </c>
       <c r="R14" t="n">
-        <v>7400452</v>
+        <v>7400295</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1948,7 +1948,7 @@
         <v>128944678</v>
       </c>
       <c r="B15" t="n">
-        <v>92856</v>
+        <v>92858</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>128944673</v>
       </c>
       <c r="B16" t="n">
-        <v>90575</v>
+        <v>90577</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         <v>128944685</v>
       </c>
       <c r="B17" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>128944679</v>
       </c>
       <c r="B18" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>128944693</v>
       </c>
       <c r="B19" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>128944681</v>
       </c>
       <c r="B20" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>128944672</v>
       </c>
       <c r="B21" t="n">
-        <v>91730</v>
+        <v>91732</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>128970462</v>
       </c>
       <c r="B22" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>128970454</v>
       </c>
       <c r="B23" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>128970459</v>
       </c>
       <c r="B24" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>128970458</v>
       </c>
       <c r="B25" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3012,32 +3012,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128970447</v>
+        <v>128970445</v>
       </c>
       <c r="B26" t="n">
-        <v>92837</v>
+        <v>92831</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4366</v>
+        <v>4365</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>730515</v>
+        <v>730387</v>
       </c>
       <c r="R26" t="n">
-        <v>7400280</v>
+        <v>7400491</v>
       </c>
       <c r="S26" t="n">
         <v>3</v>
@@ -3109,32 +3109,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128970445</v>
+        <v>128970447</v>
       </c>
       <c r="B27" t="n">
-        <v>92829</v>
+        <v>92839</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4365</v>
+        <v>4366</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3144,10 +3144,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>730387</v>
+        <v>730515</v>
       </c>
       <c r="R27" t="n">
-        <v>7400491</v>
+        <v>7400280</v>
       </c>
       <c r="S27" t="n">
         <v>3</v>
@@ -3209,7 +3209,7 @@
         <v>128970464</v>
       </c>
       <c r="B28" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3303,32 +3303,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128970444</v>
+        <v>128970461</v>
       </c>
       <c r="B29" t="n">
-        <v>92809</v>
+        <v>92827</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6055</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3338,10 +3338,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>730530</v>
+        <v>730490</v>
       </c>
       <c r="R29" t="n">
-        <v>7400285</v>
+        <v>7400286</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3400,32 +3400,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128970443</v>
+        <v>128970444</v>
       </c>
       <c r="B30" t="n">
-        <v>79633</v>
+        <v>92811</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229821</v>
+        <v>6055</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3435,10 +3435,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>730506</v>
+        <v>730530</v>
       </c>
       <c r="R30" t="n">
-        <v>7400283</v>
+        <v>7400285</v>
       </c>
       <c r="S30" t="n">
         <v>3</v>
@@ -3497,32 +3497,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128970461</v>
+        <v>128970456</v>
       </c>
       <c r="B31" t="n">
-        <v>92825</v>
+        <v>78801</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3532,10 +3532,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>730490</v>
+        <v>730514</v>
       </c>
       <c r="R31" t="n">
-        <v>7400286</v>
+        <v>7400402</v>
       </c>
       <c r="S31" t="n">
         <v>3</v>
@@ -3594,10 +3594,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128970456</v>
+        <v>128970443</v>
       </c>
       <c r="B32" t="n">
-        <v>78800</v>
+        <v>79634</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3605,21 +3605,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>730514</v>
+        <v>730506</v>
       </c>
       <c r="R32" t="n">
-        <v>7400402</v>
+        <v>7400283</v>
       </c>
       <c r="S32" t="n">
         <v>3</v>
@@ -3691,10 +3691,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128970460</v>
+        <v>128970453</v>
       </c>
       <c r="B33" t="n">
-        <v>79122</v>
+        <v>78802</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3702,21 +3702,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>864</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3726,10 +3726,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>730589</v>
+        <v>730495</v>
       </c>
       <c r="R33" t="n">
-        <v>7400431</v>
+        <v>7400399</v>
       </c>
       <c r="S33" t="n">
         <v>3</v>
@@ -3788,10 +3788,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128970453</v>
+        <v>128970460</v>
       </c>
       <c r="B34" t="n">
-        <v>78801</v>
+        <v>79123</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3799,21 +3799,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>864</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3823,10 +3823,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>730495</v>
+        <v>730589</v>
       </c>
       <c r="R34" t="n">
-        <v>7400399</v>
+        <v>7400431</v>
       </c>
       <c r="S34" t="n">
         <v>3</v>
@@ -3888,7 +3888,7 @@
         <v>128970457</v>
       </c>
       <c r="B35" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>128970449</v>
       </c>
       <c r="B36" t="n">
-        <v>97581</v>
+        <v>97583</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4079,32 +4079,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128970463</v>
+        <v>128970441</v>
       </c>
       <c r="B37" t="n">
-        <v>92825</v>
+        <v>79634</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4114,10 +4114,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>730531</v>
+        <v>730604</v>
       </c>
       <c r="R37" t="n">
-        <v>7400330</v>
+        <v>7400290</v>
       </c>
       <c r="S37" t="n">
         <v>3</v>
@@ -4176,10 +4176,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128970441</v>
+        <v>128970452</v>
       </c>
       <c r="B38" t="n">
-        <v>79633</v>
+        <v>78802</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4187,21 +4187,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4211,10 +4211,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>730604</v>
+        <v>730572</v>
       </c>
       <c r="R38" t="n">
-        <v>7400290</v>
+        <v>7400289</v>
       </c>
       <c r="S38" t="n">
         <v>3</v>
@@ -4273,32 +4273,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128970452</v>
+        <v>128970463</v>
       </c>
       <c r="B39" t="n">
-        <v>78801</v>
+        <v>92827</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4308,10 +4308,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>730572</v>
+        <v>730531</v>
       </c>
       <c r="R39" t="n">
-        <v>7400289</v>
+        <v>7400330</v>
       </c>
       <c r="S39" t="n">
         <v>3</v>
@@ -4373,7 +4373,7 @@
         <v>128970455</v>
       </c>
       <c r="B40" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>128970450</v>
       </c>
       <c r="B41" t="n">
-        <v>91596</v>
+        <v>91598</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>128970440</v>
       </c>
       <c r="B42" t="n">
-        <v>79633</v>
+        <v>79634</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>128970442</v>
       </c>
       <c r="B43" t="n">
-        <v>79633</v>
+        <v>79634</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>128970448</v>
       </c>
       <c r="B44" t="n">
-        <v>92837</v>
+        <v>92839</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 44203-2025 artfynd.xlsx
+++ b/artfynd/A 44203-2025 artfynd.xlsx
@@ -1075,7 +1075,7 @@
         <v>128944692</v>
       </c>
       <c r="B6" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>128944690</v>
       </c>
       <c r="B8" t="n">
-        <v>91718</v>
+        <v>91722</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128944686</v>
+        <v>128944674</v>
       </c>
       <c r="B12" t="n">
-        <v>78801</v>
+        <v>90581</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1665,21 +1665,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>730518</v>
+        <v>730365</v>
       </c>
       <c r="R12" t="n">
-        <v>7400367</v>
+        <v>7400452</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1751,32 +1751,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128944674</v>
+        <v>128944691</v>
       </c>
       <c r="B13" t="n">
-        <v>90577</v>
+        <v>92831</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>730365</v>
+        <v>730498</v>
       </c>
       <c r="R13" t="n">
-        <v>7400452</v>
+        <v>7400295</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1848,32 +1848,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128944691</v>
+        <v>128944686</v>
       </c>
       <c r="B14" t="n">
-        <v>92827</v>
+        <v>78801</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>730498</v>
+        <v>730518</v>
       </c>
       <c r="R14" t="n">
-        <v>7400295</v>
+        <v>7400367</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1945,32 +1945,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128944678</v>
+        <v>128944673</v>
       </c>
       <c r="B15" t="n">
-        <v>92858</v>
+        <v>90581</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>232140</v>
+        <v>1962</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>730462</v>
+        <v>730476</v>
       </c>
       <c r="R15" t="n">
-        <v>7400313</v>
+        <v>7400283</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2042,32 +2042,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128944673</v>
+        <v>128944678</v>
       </c>
       <c r="B16" t="n">
-        <v>90577</v>
+        <v>92862</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1962</v>
+        <v>232140</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>730476</v>
+        <v>730462</v>
       </c>
       <c r="R16" t="n">
-        <v>7400283</v>
+        <v>7400313</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2336,7 +2336,7 @@
         <v>128944693</v>
       </c>
       <c r="B19" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>128944672</v>
       </c>
       <c r="B21" t="n">
-        <v>91732</v>
+        <v>91736</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>128970462</v>
       </c>
       <c r="B22" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>128970445</v>
       </c>
       <c r="B26" t="n">
-        <v>92831</v>
+        <v>92835</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>128970447</v>
       </c>
       <c r="B27" t="n">
-        <v>92839</v>
+        <v>92843</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>128970464</v>
       </c>
       <c r="B28" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3303,32 +3303,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128970461</v>
+        <v>128970443</v>
       </c>
       <c r="B29" t="n">
-        <v>92827</v>
+        <v>79634</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3338,10 +3338,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>730490</v>
+        <v>730506</v>
       </c>
       <c r="R29" t="n">
-        <v>7400286</v>
+        <v>7400283</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3403,7 +3403,7 @@
         <v>128970444</v>
       </c>
       <c r="B30" t="n">
-        <v>92811</v>
+        <v>92815</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3497,32 +3497,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128970456</v>
+        <v>128970461</v>
       </c>
       <c r="B31" t="n">
-        <v>78801</v>
+        <v>92831</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3532,10 +3532,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>730514</v>
+        <v>730490</v>
       </c>
       <c r="R31" t="n">
-        <v>7400402</v>
+        <v>7400286</v>
       </c>
       <c r="S31" t="n">
         <v>3</v>
@@ -3594,10 +3594,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128970443</v>
+        <v>128970456</v>
       </c>
       <c r="B32" t="n">
-        <v>79634</v>
+        <v>78801</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3605,21 +3605,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>730506</v>
+        <v>730514</v>
       </c>
       <c r="R32" t="n">
-        <v>7400283</v>
+        <v>7400402</v>
       </c>
       <c r="S32" t="n">
         <v>3</v>
@@ -3691,10 +3691,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128970453</v>
+        <v>128970460</v>
       </c>
       <c r="B33" t="n">
-        <v>78802</v>
+        <v>79123</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3702,21 +3702,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>864</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3726,10 +3726,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>730495</v>
+        <v>730589</v>
       </c>
       <c r="R33" t="n">
-        <v>7400399</v>
+        <v>7400431</v>
       </c>
       <c r="S33" t="n">
         <v>3</v>
@@ -3788,10 +3788,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128970460</v>
+        <v>128970453</v>
       </c>
       <c r="B34" t="n">
-        <v>79123</v>
+        <v>78802</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3799,21 +3799,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>864</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3823,10 +3823,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>730589</v>
+        <v>730495</v>
       </c>
       <c r="R34" t="n">
-        <v>7400431</v>
+        <v>7400399</v>
       </c>
       <c r="S34" t="n">
         <v>3</v>
@@ -3885,32 +3885,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128970457</v>
+        <v>128970449</v>
       </c>
       <c r="B35" t="n">
-        <v>78801</v>
+        <v>97587</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>221945</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3920,10 +3920,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>730492</v>
+        <v>730553</v>
       </c>
       <c r="R35" t="n">
-        <v>7400398</v>
+        <v>7400437</v>
       </c>
       <c r="S35" t="n">
         <v>3</v>
@@ -3982,32 +3982,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128970449</v>
+        <v>128970457</v>
       </c>
       <c r="B36" t="n">
-        <v>97583</v>
+        <v>78801</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221945</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4017,10 +4017,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>730553</v>
+        <v>730492</v>
       </c>
       <c r="R36" t="n">
-        <v>7400437</v>
+        <v>7400398</v>
       </c>
       <c r="S36" t="n">
         <v>3</v>
@@ -4079,32 +4079,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128970441</v>
+        <v>128970463</v>
       </c>
       <c r="B37" t="n">
-        <v>79634</v>
+        <v>92831</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4114,10 +4114,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>730604</v>
+        <v>730531</v>
       </c>
       <c r="R37" t="n">
-        <v>7400290</v>
+        <v>7400330</v>
       </c>
       <c r="S37" t="n">
         <v>3</v>
@@ -4273,32 +4273,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128970463</v>
+        <v>128970441</v>
       </c>
       <c r="B39" t="n">
-        <v>92827</v>
+        <v>79634</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4308,10 +4308,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>730531</v>
+        <v>730604</v>
       </c>
       <c r="R39" t="n">
-        <v>7400330</v>
+        <v>7400290</v>
       </c>
       <c r="S39" t="n">
         <v>3</v>
@@ -4470,7 +4470,7 @@
         <v>128970450</v>
       </c>
       <c r="B41" t="n">
-        <v>91598</v>
+        <v>91602</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>128970448</v>
       </c>
       <c r="B44" t="n">
-        <v>92839</v>
+        <v>92843</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 44203-2025 artfynd.xlsx
+++ b/artfynd/A 44203-2025 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128944684</v>
+        <v>128944682</v>
       </c>
       <c r="B3" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730648</v>
+        <v>730487</v>
       </c>
       <c r="R3" t="n">
-        <v>7400352</v>
+        <v>7400456</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -878,10 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128944682</v>
+        <v>128944684</v>
       </c>
       <c r="B4" t="n">
-        <v>78802</v>
+        <v>78801</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -889,21 +889,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730487</v>
+        <v>730648</v>
       </c>
       <c r="R4" t="n">
-        <v>7400456</v>
+        <v>7400352</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1075,7 +1075,7 @@
         <v>128944692</v>
       </c>
       <c r="B6" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>128944690</v>
       </c>
       <c r="B8" t="n">
-        <v>91722</v>
+        <v>91723</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1654,32 +1654,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128944674</v>
+        <v>128944691</v>
       </c>
       <c r="B12" t="n">
-        <v>90581</v>
+        <v>92832</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>730365</v>
+        <v>730498</v>
       </c>
       <c r="R12" t="n">
-        <v>7400452</v>
+        <v>7400295</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1751,32 +1751,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128944691</v>
+        <v>128944674</v>
       </c>
       <c r="B13" t="n">
-        <v>92831</v>
+        <v>90582</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>730498</v>
+        <v>730365</v>
       </c>
       <c r="R13" t="n">
-        <v>7400295</v>
+        <v>7400452</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1948,7 +1948,7 @@
         <v>128944673</v>
       </c>
       <c r="B15" t="n">
-        <v>90581</v>
+        <v>90582</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2042,32 +2042,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128944678</v>
+        <v>128944685</v>
       </c>
       <c r="B16" t="n">
-        <v>92862</v>
+        <v>78801</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>232140</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>730462</v>
+        <v>730663</v>
       </c>
       <c r="R16" t="n">
-        <v>7400313</v>
+        <v>7400366</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2139,32 +2139,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128944685</v>
+        <v>128944678</v>
       </c>
       <c r="B17" t="n">
-        <v>78801</v>
+        <v>92863</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>232140</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2174,10 +2174,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>730663</v>
+        <v>730462</v>
       </c>
       <c r="R17" t="n">
-        <v>7400366</v>
+        <v>7400313</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2333,32 +2333,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128944693</v>
+        <v>128944681</v>
       </c>
       <c r="B19" t="n">
-        <v>92831</v>
+        <v>78802</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2368,10 +2368,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>730500</v>
+        <v>730491</v>
       </c>
       <c r="R19" t="n">
-        <v>7400421</v>
+        <v>7400393</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2430,32 +2430,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128944681</v>
+        <v>128944693</v>
       </c>
       <c r="B20" t="n">
-        <v>78802</v>
+        <v>92832</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>730491</v>
+        <v>730500</v>
       </c>
       <c r="R20" t="n">
-        <v>7400393</v>
+        <v>7400421</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2530,7 +2530,7 @@
         <v>128944672</v>
       </c>
       <c r="B21" t="n">
-        <v>91736</v>
+        <v>91737</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>128970462</v>
       </c>
       <c r="B22" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>128970445</v>
       </c>
       <c r="B26" t="n">
-        <v>92835</v>
+        <v>92836</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>128970447</v>
       </c>
       <c r="B27" t="n">
-        <v>92843</v>
+        <v>92844</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>128970464</v>
       </c>
       <c r="B28" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3303,32 +3303,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128970443</v>
+        <v>128970444</v>
       </c>
       <c r="B29" t="n">
-        <v>79634</v>
+        <v>92816</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229821</v>
+        <v>6055</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3338,10 +3338,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>730506</v>
+        <v>730530</v>
       </c>
       <c r="R29" t="n">
-        <v>7400283</v>
+        <v>7400285</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3400,32 +3400,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128970444</v>
+        <v>128970443</v>
       </c>
       <c r="B30" t="n">
-        <v>92815</v>
+        <v>79634</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6055</v>
+        <v>229821</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3435,10 +3435,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>730530</v>
+        <v>730506</v>
       </c>
       <c r="R30" t="n">
-        <v>7400285</v>
+        <v>7400283</v>
       </c>
       <c r="S30" t="n">
         <v>3</v>
@@ -3500,7 +3500,7 @@
         <v>128970461</v>
       </c>
       <c r="B31" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3691,10 +3691,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128970460</v>
+        <v>128970453</v>
       </c>
       <c r="B33" t="n">
-        <v>79123</v>
+        <v>78802</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3702,21 +3702,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>864</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3726,10 +3726,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>730589</v>
+        <v>730495</v>
       </c>
       <c r="R33" t="n">
-        <v>7400431</v>
+        <v>7400399</v>
       </c>
       <c r="S33" t="n">
         <v>3</v>
@@ -3788,10 +3788,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128970453</v>
+        <v>128970460</v>
       </c>
       <c r="B34" t="n">
-        <v>78802</v>
+        <v>79123</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3799,21 +3799,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>864</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3823,10 +3823,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>730495</v>
+        <v>730589</v>
       </c>
       <c r="R34" t="n">
-        <v>7400399</v>
+        <v>7400431</v>
       </c>
       <c r="S34" t="n">
         <v>3</v>
@@ -3885,32 +3885,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128970449</v>
+        <v>128970457</v>
       </c>
       <c r="B35" t="n">
-        <v>97587</v>
+        <v>78801</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221945</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3920,10 +3920,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>730553</v>
+        <v>730492</v>
       </c>
       <c r="R35" t="n">
-        <v>7400437</v>
+        <v>7400398</v>
       </c>
       <c r="S35" t="n">
         <v>3</v>
@@ -3982,32 +3982,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128970457</v>
+        <v>128970449</v>
       </c>
       <c r="B36" t="n">
-        <v>78801</v>
+        <v>97595</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>221945</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4017,10 +4017,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>730492</v>
+        <v>730553</v>
       </c>
       <c r="R36" t="n">
-        <v>7400398</v>
+        <v>7400437</v>
       </c>
       <c r="S36" t="n">
         <v>3</v>
@@ -4079,32 +4079,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128970463</v>
+        <v>128970441</v>
       </c>
       <c r="B37" t="n">
-        <v>92831</v>
+        <v>79634</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4114,10 +4114,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>730531</v>
+        <v>730604</v>
       </c>
       <c r="R37" t="n">
-        <v>7400330</v>
+        <v>7400290</v>
       </c>
       <c r="S37" t="n">
         <v>3</v>
@@ -4273,32 +4273,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128970441</v>
+        <v>128970463</v>
       </c>
       <c r="B39" t="n">
-        <v>79634</v>
+        <v>92832</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4308,10 +4308,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>730604</v>
+        <v>730531</v>
       </c>
       <c r="R39" t="n">
-        <v>7400290</v>
+        <v>7400330</v>
       </c>
       <c r="S39" t="n">
         <v>3</v>
@@ -4470,7 +4470,7 @@
         <v>128970450</v>
       </c>
       <c r="B41" t="n">
-        <v>91602</v>
+        <v>91603</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>128970448</v>
       </c>
       <c r="B44" t="n">
-        <v>92843</v>
+        <v>92844</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 44203-2025 artfynd.xlsx
+++ b/artfynd/A 44203-2025 artfynd.xlsx
@@ -2624,32 +2624,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128970462</v>
+        <v>128970454</v>
       </c>
       <c r="B22" t="n">
-        <v>92832</v>
+        <v>78801</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>730496</v>
+        <v>730523</v>
       </c>
       <c r="R22" t="n">
-        <v>7400291</v>
+        <v>7400319</v>
       </c>
       <c r="S22" t="n">
         <v>3</v>
@@ -2721,32 +2721,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128970454</v>
+        <v>128970462</v>
       </c>
       <c r="B23" t="n">
-        <v>78801</v>
+        <v>92832</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2756,10 +2756,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>730523</v>
+        <v>730496</v>
       </c>
       <c r="R23" t="n">
-        <v>7400319</v>
+        <v>7400291</v>
       </c>
       <c r="S23" t="n">
         <v>3</v>
@@ -3303,32 +3303,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128970444</v>
+        <v>128970456</v>
       </c>
       <c r="B29" t="n">
-        <v>92816</v>
+        <v>78801</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6055</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3338,10 +3338,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>730530</v>
+        <v>730514</v>
       </c>
       <c r="R29" t="n">
-        <v>7400285</v>
+        <v>7400402</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3400,32 +3400,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128970443</v>
+        <v>128970444</v>
       </c>
       <c r="B30" t="n">
-        <v>79634</v>
+        <v>92816</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229821</v>
+        <v>6055</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3435,10 +3435,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>730506</v>
+        <v>730530</v>
       </c>
       <c r="R30" t="n">
-        <v>7400283</v>
+        <v>7400285</v>
       </c>
       <c r="S30" t="n">
         <v>3</v>
@@ -3594,10 +3594,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128970456</v>
+        <v>128970443</v>
       </c>
       <c r="B32" t="n">
-        <v>78801</v>
+        <v>79634</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3605,21 +3605,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>730514</v>
+        <v>730506</v>
       </c>
       <c r="R32" t="n">
-        <v>7400402</v>
+        <v>7400283</v>
       </c>
       <c r="S32" t="n">
         <v>3</v>
@@ -4079,32 +4079,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128970441</v>
+        <v>128970463</v>
       </c>
       <c r="B37" t="n">
-        <v>79634</v>
+        <v>92832</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4114,10 +4114,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>730604</v>
+        <v>730531</v>
       </c>
       <c r="R37" t="n">
-        <v>7400290</v>
+        <v>7400330</v>
       </c>
       <c r="S37" t="n">
         <v>3</v>
@@ -4176,10 +4176,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128970452</v>
+        <v>128970441</v>
       </c>
       <c r="B38" t="n">
-        <v>78802</v>
+        <v>79634</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4187,21 +4187,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4211,10 +4211,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>730572</v>
+        <v>730604</v>
       </c>
       <c r="R38" t="n">
-        <v>7400289</v>
+        <v>7400290</v>
       </c>
       <c r="S38" t="n">
         <v>3</v>
@@ -4273,32 +4273,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128970463</v>
+        <v>128970452</v>
       </c>
       <c r="B39" t="n">
-        <v>92832</v>
+        <v>78802</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4308,10 +4308,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>730531</v>
+        <v>730572</v>
       </c>
       <c r="R39" t="n">
-        <v>7400330</v>
+        <v>7400289</v>
       </c>
       <c r="S39" t="n">
         <v>3</v>
